--- a/kream_test_data.xlsx
+++ b/kream_test_data.xlsx
@@ -20,8 +20,8 @@
     <numFmt numFmtId="165" formatCode="yy/m/d"/>
     <numFmt numFmtId="166" formatCode="yyyy\-mm\-dd"/>
     <numFmt numFmtId="167" formatCode="yyyy\-mm\-dd\ hh:mm:ss"/>
-    <numFmt numFmtId="168" formatCode="yyyy-mm-dd h:mm:ss"/>
-    <numFmt numFmtId="169" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="168" formatCode="YYYY-MM-DD HH:MM:SS"/>
+    <numFmt numFmtId="169" formatCode="yyyy-mm-dd h:mm:ss"/>
   </numFmts>
   <fonts count="27">
     <font>
@@ -666,7 +666,7 @@
       <alignment vertical="center"/>
     </xf>
   </cellStyleXfs>
-  <cellXfs count="24">
+  <cellXfs count="25">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
@@ -716,7 +716,8 @@
     <xf numFmtId="0" fontId="26" fillId="0" borderId="11" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="169" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
+    <xf numFmtId="168" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
   </cellXfs>
   <cellStyles count="49">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -1097,8 +1098,8 @@
       <c r="E2" t="n">
         <v>0</v>
       </c>
-      <c r="F2" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F2" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="3">
@@ -1123,8 +1124,8 @@
       <c r="E3" t="n">
         <v>0</v>
       </c>
-      <c r="F3" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F3" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="4">
@@ -1149,8 +1150,8 @@
       <c r="E4" t="n">
         <v>0</v>
       </c>
-      <c r="F4" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F4" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="5">
@@ -1175,8 +1176,8 @@
       <c r="E5" t="n">
         <v>0</v>
       </c>
-      <c r="F5" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F5" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="6">
@@ -1201,8 +1202,8 @@
       <c r="E6" t="n">
         <v>0</v>
       </c>
-      <c r="F6" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F6" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="7">
@@ -1227,8 +1228,8 @@
       <c r="E7" t="n">
         <v>0</v>
       </c>
-      <c r="F7" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F7" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="8">
@@ -1253,8 +1254,8 @@
       <c r="E8" t="n">
         <v>0</v>
       </c>
-      <c r="F8" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F8" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="9">
@@ -1279,8 +1280,8 @@
       <c r="E9" t="n">
         <v>0</v>
       </c>
-      <c r="F9" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F9" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="10">
@@ -1305,8 +1306,8 @@
       <c r="E10" t="n">
         <v>0</v>
       </c>
-      <c r="F10" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F10" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="11">
@@ -1331,8 +1332,8 @@
       <c r="E11" t="n">
         <v>0</v>
       </c>
-      <c r="F11" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F11" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="12">
@@ -1357,8 +1358,8 @@
       <c r="E12" t="n">
         <v>0</v>
       </c>
-      <c r="F12" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F12" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="13">
@@ -1383,8 +1384,8 @@
       <c r="E13" t="n">
         <v>0</v>
       </c>
-      <c r="F13" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F13" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="14">
@@ -1409,8 +1410,8 @@
       <c r="E14" t="n">
         <v>0</v>
       </c>
-      <c r="F14" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F14" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="15">
@@ -1435,8 +1436,8 @@
       <c r="E15" t="n">
         <v>0</v>
       </c>
-      <c r="F15" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F15" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="16">
@@ -1461,8 +1462,8 @@
       <c r="E16" t="n">
         <v>0</v>
       </c>
-      <c r="F16" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F16" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="17">
@@ -1487,8 +1488,8 @@
       <c r="E17" t="n">
         <v>0</v>
       </c>
-      <c r="F17" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F17" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="18">
@@ -1513,8 +1514,8 @@
       <c r="E18" t="n">
         <v>0</v>
       </c>
-      <c r="F18" s="23" t="n">
-        <v>45476.56670138889</v>
+      <c r="F18" s="24" t="n">
+        <v>45476.58987268519</v>
       </c>
     </row>
     <row r="19">
@@ -1539,8 +1540,8 @@
       <c r="E19" t="n">
         <v>0</v>
       </c>
-      <c r="F19" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F19" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="20">
@@ -1565,8 +1566,8 @@
       <c r="E20" t="n">
         <v>0</v>
       </c>
-      <c r="F20" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F20" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="21">
@@ -1591,8 +1592,8 @@
       <c r="E21" t="n">
         <v>0</v>
       </c>
-      <c r="F21" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F21" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="22">
@@ -1617,8 +1618,8 @@
       <c r="E22" t="n">
         <v>0</v>
       </c>
-      <c r="F22" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F22" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="23">
@@ -1643,8 +1644,8 @@
       <c r="E23" t="n">
         <v>0</v>
       </c>
-      <c r="F23" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F23" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="24">
@@ -1669,8 +1670,8 @@
       <c r="E24" t="n">
         <v>0</v>
       </c>
-      <c r="F24" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F24" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="25">
@@ -1695,8 +1696,8 @@
       <c r="E25" t="n">
         <v>0</v>
       </c>
-      <c r="F25" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F25" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="26">
@@ -1721,8 +1722,8 @@
       <c r="E26" t="n">
         <v>0</v>
       </c>
-      <c r="F26" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F26" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="27">
@@ -1747,8 +1748,8 @@
       <c r="E27" t="n">
         <v>0</v>
       </c>
-      <c r="F27" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F27" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="28">
@@ -1773,8 +1774,8 @@
       <c r="E28" t="n">
         <v>0</v>
       </c>
-      <c r="F28" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F28" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="29">
@@ -1799,8 +1800,8 @@
       <c r="E29" t="n">
         <v>0</v>
       </c>
-      <c r="F29" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F29" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="30">
@@ -1825,8 +1826,8 @@
       <c r="E30" t="n">
         <v>0</v>
       </c>
-      <c r="F30" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F30" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="31">
@@ -1851,8 +1852,8 @@
       <c r="E31" t="n">
         <v>0</v>
       </c>
-      <c r="F31" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F31" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="32">
@@ -1877,8 +1878,8 @@
       <c r="E32" t="n">
         <v>0</v>
       </c>
-      <c r="F32" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F32" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="33">
@@ -1903,8 +1904,8 @@
       <c r="E33" t="n">
         <v>0</v>
       </c>
-      <c r="F33" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F33" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="34">
@@ -1929,8 +1930,8 @@
       <c r="E34" t="n">
         <v>0</v>
       </c>
-      <c r="F34" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F34" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="35">
@@ -1955,8 +1956,8 @@
       <c r="E35" t="n">
         <v>0</v>
       </c>
-      <c r="F35" s="23" t="n">
-        <v>45476.56671296297</v>
+      <c r="F35" s="24" t="n">
+        <v>45476.58989583333</v>
       </c>
     </row>
     <row r="36">
@@ -1981,8 +1982,8 @@
       <c r="E36" t="n">
         <v>0</v>
       </c>
-      <c r="F36" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F36" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="37">
@@ -2007,8 +2008,8 @@
       <c r="E37" t="n">
         <v>0</v>
       </c>
-      <c r="F37" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F37" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="38">
@@ -2033,8 +2034,8 @@
       <c r="E38" t="n">
         <v>0</v>
       </c>
-      <c r="F38" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F38" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="39">
@@ -2059,8 +2060,8 @@
       <c r="E39" t="n">
         <v>0</v>
       </c>
-      <c r="F39" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F39" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="40">
@@ -2085,8 +2086,8 @@
       <c r="E40" t="n">
         <v>0</v>
       </c>
-      <c r="F40" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F40" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="41">
@@ -2111,8 +2112,8 @@
       <c r="E41" t="n">
         <v>0</v>
       </c>
-      <c r="F41" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F41" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="42">
@@ -2137,8 +2138,8 @@
       <c r="E42" t="n">
         <v>0</v>
       </c>
-      <c r="F42" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F42" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="43">
@@ -2163,8 +2164,8 @@
       <c r="E43" t="n">
         <v>0</v>
       </c>
-      <c r="F43" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F43" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="44">
@@ -2189,8 +2190,8 @@
       <c r="E44" t="n">
         <v>0</v>
       </c>
-      <c r="F44" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F44" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="45">
@@ -2215,8 +2216,8 @@
       <c r="E45" t="n">
         <v>0</v>
       </c>
-      <c r="F45" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F45" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="46">
@@ -2241,8 +2242,8 @@
       <c r="E46" t="n">
         <v>0</v>
       </c>
-      <c r="F46" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F46" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="47">
@@ -2267,8 +2268,8 @@
       <c r="E47" t="n">
         <v>0</v>
       </c>
-      <c r="F47" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F47" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="48">
@@ -2293,8 +2294,8 @@
       <c r="E48" t="n">
         <v>0</v>
       </c>
-      <c r="F48" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F48" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="49">
@@ -2319,8 +2320,8 @@
       <c r="E49" t="n">
         <v>0</v>
       </c>
-      <c r="F49" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F49" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="50">
@@ -2345,8 +2346,8 @@
       <c r="E50" t="n">
         <v>0</v>
       </c>
-      <c r="F50" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F50" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="51">
@@ -2371,8 +2372,8 @@
       <c r="E51" t="n">
         <v>0</v>
       </c>
-      <c r="F51" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F51" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="52">
@@ -2397,8 +2398,8 @@
       <c r="E52" t="n">
         <v>0</v>
       </c>
-      <c r="F52" s="23" t="n">
-        <v>45476.56672453704</v>
+      <c r="F52" s="24" t="n">
+        <v>45476.5899074074</v>
       </c>
     </row>
     <row r="53">
@@ -2423,8 +2424,8 @@
       <c r="E53" t="n">
         <v>0</v>
       </c>
-      <c r="F53" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F53" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="54">
@@ -2449,8 +2450,8 @@
       <c r="E54" t="n">
         <v>0</v>
       </c>
-      <c r="F54" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F54" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="55">
@@ -2475,8 +2476,8 @@
       <c r="E55" t="n">
         <v>0</v>
       </c>
-      <c r="F55" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F55" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="56">
@@ -2501,8 +2502,8 @@
       <c r="E56" t="n">
         <v>0</v>
       </c>
-      <c r="F56" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F56" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="57">
@@ -2527,8 +2528,8 @@
       <c r="E57" t="n">
         <v>0</v>
       </c>
-      <c r="F57" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F57" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="58">
@@ -2553,8 +2554,8 @@
       <c r="E58" t="n">
         <v>0</v>
       </c>
-      <c r="F58" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F58" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="59">
@@ -2579,8 +2580,8 @@
       <c r="E59" t="n">
         <v>0</v>
       </c>
-      <c r="F59" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F59" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="60">
@@ -2605,8 +2606,8 @@
       <c r="E60" t="n">
         <v>0</v>
       </c>
-      <c r="F60" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F60" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="61">
@@ -2631,8 +2632,8 @@
       <c r="E61" t="n">
         <v>0</v>
       </c>
-      <c r="F61" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F61" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="62">
@@ -2657,8 +2658,8 @@
       <c r="E62" t="n">
         <v>0</v>
       </c>
-      <c r="F62" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F62" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="63">
@@ -2683,8 +2684,8 @@
       <c r="E63" t="n">
         <v>0</v>
       </c>
-      <c r="F63" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F63" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="64">
@@ -2709,8 +2710,8 @@
       <c r="E64" t="n">
         <v>0</v>
       </c>
-      <c r="F64" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F64" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="65">
@@ -2735,8 +2736,8 @@
       <c r="E65" t="n">
         <v>0</v>
       </c>
-      <c r="F65" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F65" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="66">
@@ -2761,8 +2762,8 @@
       <c r="E66" t="n">
         <v>0</v>
       </c>
-      <c r="F66" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F66" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="67">
@@ -2787,8 +2788,8 @@
       <c r="E67" t="n">
         <v>0</v>
       </c>
-      <c r="F67" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F67" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="68">
@@ -2813,8 +2814,8 @@
       <c r="E68" t="n">
         <v>0</v>
       </c>
-      <c r="F68" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F68" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="69">
@@ -2839,8 +2840,8 @@
       <c r="E69" t="n">
         <v>0</v>
       </c>
-      <c r="F69" s="23" t="n">
-        <v>45476.56673611111</v>
+      <c r="F69" s="24" t="n">
+        <v>45476.58991898148</v>
       </c>
     </row>
     <row r="70">
@@ -2865,8 +2866,8 @@
       <c r="E70" t="n">
         <v>0</v>
       </c>
-      <c r="F70" s="23" t="n">
-        <v>45476.56675925926</v>
+      <c r="F70" s="24" t="n">
+        <v>45476.58993055556</v>
       </c>
     </row>
     <row r="71">
@@ -2891,8 +2892,8 @@
       <c r="E71" t="n">
         <v>0</v>
       </c>
-      <c r="F71" s="23" t="n">
-        <v>45476.56675925926</v>
+      <c r="F71" s="24" t="n">
+        <v>45476.58993055556</v>
       </c>
     </row>
     <row r="72">
@@ -2917,8 +2918,8 @@
       <c r="E72" t="n">
         <v>0</v>
       </c>
-      <c r="F72" s="23" t="n">
-        <v>45476.56675925926</v>
+      <c r="F72" s="24" t="n">
+        <v>45476.58993055556</v>
       </c>
     </row>
     <row r="73">
@@ -2943,8 +2944,8 @@
       <c r="E73" t="n">
         <v>0</v>
       </c>
-      <c r="F73" s="23" t="n">
-        <v>45476.56675925926</v>
+      <c r="F73" s="24" t="n">
+        <v>45476.58993055556</v>
       </c>
     </row>
     <row r="74">
@@ -2969,8 +2970,8 @@
       <c r="E74" t="n">
         <v>0</v>
       </c>
-      <c r="F74" s="23" t="n">
-        <v>45476.56675925926</v>
+      <c r="F74" s="24" t="n">
+        <v>45476.58993055556</v>
       </c>
     </row>
     <row r="75">
@@ -2995,8 +2996,8 @@
       <c r="E75" t="n">
         <v>0</v>
       </c>
-      <c r="F75" s="23" t="n">
-        <v>45476.56675925926</v>
+      <c r="F75" s="24" t="n">
+        <v>45476.58993055556</v>
       </c>
     </row>
     <row r="76">
@@ -3021,8 +3022,8 @@
       <c r="E76" t="n">
         <v>0</v>
       </c>
-      <c r="F76" s="23" t="n">
-        <v>45476.56675925926</v>
+      <c r="F76" s="24" t="n">
+        <v>45476.58993055556</v>
       </c>
     </row>
     <row r="77">
@@ -3047,8 +3048,8 @@
       <c r="E77" t="n">
         <v>0</v>
       </c>
-      <c r="F77" s="23" t="n">
-        <v>45476.56675925926</v>
+      <c r="F77" s="24" t="n">
+        <v>45476.58993055556</v>
       </c>
     </row>
     <row r="78">
@@ -3073,8 +3074,8 @@
       <c r="E78" t="n">
         <v>0</v>
       </c>
-      <c r="F78" s="23" t="n">
-        <v>45476.56675925926</v>
+      <c r="F78" s="24" t="n">
+        <v>45476.58993055556</v>
       </c>
     </row>
     <row r="79">
@@ -3099,8 +3100,8 @@
       <c r="E79" t="n">
         <v>0</v>
       </c>
-      <c r="F79" s="23" t="n">
-        <v>45476.56675925926</v>
+      <c r="F79" s="24" t="n">
+        <v>45476.58993055556</v>
       </c>
     </row>
     <row r="80">
@@ -3125,8 +3126,8 @@
       <c r="E80" t="n">
         <v>0</v>
       </c>
-      <c r="F80" s="23" t="n">
-        <v>45476.56677083333</v>
+      <c r="F80" s="24" t="n">
+        <v>45476.5899537037</v>
       </c>
     </row>
     <row r="81">
@@ -3151,8 +3152,8 @@
       <c r="E81" t="n">
         <v>0</v>
       </c>
-      <c r="F81" s="23" t="n">
-        <v>45476.56677083333</v>
+      <c r="F81" s="24" t="n">
+        <v>45476.5899537037</v>
       </c>
     </row>
     <row r="82">
@@ -3177,8 +3178,8 @@
       <c r="E82" t="n">
         <v>0</v>
       </c>
-      <c r="F82" s="23" t="n">
-        <v>45476.56677083333</v>
+      <c r="F82" s="24" t="n">
+        <v>45476.5899537037</v>
       </c>
     </row>
     <row r="83">
@@ -3203,8 +3204,8 @@
       <c r="E83" t="n">
         <v>0</v>
       </c>
-      <c r="F83" s="23" t="n">
-        <v>45476.56677083333</v>
+      <c r="F83" s="24" t="n">
+        <v>45476.5899537037</v>
       </c>
     </row>
     <row r="84">
@@ -3229,8 +3230,8 @@
       <c r="E84" t="n">
         <v>0</v>
       </c>
-      <c r="F84" s="23" t="n">
-        <v>45476.56677083333</v>
+      <c r="F84" s="24" t="n">
+        <v>45476.5899537037</v>
       </c>
     </row>
     <row r="85">
@@ -3255,8 +3256,8 @@
       <c r="E85" t="n">
         <v>0</v>
       </c>
-      <c r="F85" s="23" t="n">
-        <v>45476.56677083333</v>
+      <c r="F85" s="24" t="n">
+        <v>45476.5899537037</v>
       </c>
     </row>
     <row r="86">
@@ -3281,8 +3282,8 @@
       <c r="E86" t="n">
         <v>0</v>
       </c>
-      <c r="F86" s="23" t="n">
-        <v>45476.56677083333</v>
+      <c r="F86" s="24" t="n">
+        <v>45476.5899537037</v>
       </c>
     </row>
     <row r="87">
@@ -3307,8 +3308,8 @@
       <c r="E87" t="n">
         <v>0</v>
       </c>
-      <c r="F87" s="23" t="n">
-        <v>45476.56677083333</v>
+      <c r="F87" s="24" t="n">
+        <v>45476.5899537037</v>
       </c>
     </row>
     <row r="88">
@@ -3333,8 +3334,8 @@
       <c r="E88" t="n">
         <v>0</v>
       </c>
-      <c r="F88" s="23" t="n">
-        <v>45476.56677083333</v>
+      <c r="F88" s="24" t="n">
+        <v>45476.5899537037</v>
       </c>
     </row>
     <row r="89">
@@ -3359,8 +3360,8 @@
       <c r="E89" t="n">
         <v>0</v>
       </c>
-      <c r="F89" s="23" t="n">
-        <v>45476.56677083333</v>
+      <c r="F89" s="24" t="n">
+        <v>45476.5899537037</v>
       </c>
     </row>
     <row r="90">
@@ -3385,8 +3386,8 @@
       <c r="E90" t="n">
         <v>0</v>
       </c>
-      <c r="F90" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F90" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="91">
@@ -3411,8 +3412,8 @@
       <c r="E91" t="n">
         <v>0</v>
       </c>
-      <c r="F91" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F91" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="92">
@@ -3437,8 +3438,8 @@
       <c r="E92" t="n">
         <v>0</v>
       </c>
-      <c r="F92" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F92" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="93">
@@ -3463,8 +3464,8 @@
       <c r="E93" t="n">
         <v>0</v>
       </c>
-      <c r="F93" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F93" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="94">
@@ -3489,8 +3490,8 @@
       <c r="E94" t="n">
         <v>0</v>
       </c>
-      <c r="F94" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F94" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="95">
@@ -3515,8 +3516,8 @@
       <c r="E95" t="n">
         <v>0</v>
       </c>
-      <c r="F95" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F95" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="96">
@@ -3541,8 +3542,8 @@
       <c r="E96" t="n">
         <v>0</v>
       </c>
-      <c r="F96" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F96" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="97">
@@ -3567,8 +3568,8 @@
       <c r="E97" t="n">
         <v>0</v>
       </c>
-      <c r="F97" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F97" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="98">
@@ -3593,8 +3594,8 @@
       <c r="E98" t="n">
         <v>0</v>
       </c>
-      <c r="F98" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F98" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="99">
@@ -3619,8 +3620,8 @@
       <c r="E99" t="n">
         <v>0</v>
       </c>
-      <c r="F99" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F99" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="100">
@@ -3645,8 +3646,8 @@
       <c r="E100" t="n">
         <v>0</v>
       </c>
-      <c r="F100" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F100" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="101">
@@ -3671,8 +3672,8 @@
       <c r="E101" t="n">
         <v>0</v>
       </c>
-      <c r="F101" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F101" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="102">
@@ -3697,8 +3698,8 @@
       <c r="E102" t="n">
         <v>0</v>
       </c>
-      <c r="F102" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F102" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="103">
@@ -3723,8 +3724,8 @@
       <c r="E103" t="n">
         <v>0</v>
       </c>
-      <c r="F103" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F103" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="104">
@@ -3749,8 +3750,8 @@
       <c r="E104" t="n">
         <v>0</v>
       </c>
-      <c r="F104" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F104" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="105">
@@ -3775,8 +3776,8 @@
       <c r="E105" t="n">
         <v>0</v>
       </c>
-      <c r="F105" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F105" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="106">
@@ -3801,8 +3802,8 @@
       <c r="E106" t="n">
         <v>0</v>
       </c>
-      <c r="F106" s="23" t="n">
-        <v>45476.5667824074</v>
+      <c r="F106" s="24" t="n">
+        <v>45476.58996527778</v>
       </c>
     </row>
     <row r="107">
@@ -3827,8 +3828,8 @@
       <c r="E107" t="n">
         <v>0</v>
       </c>
-      <c r="F107" s="23" t="n">
-        <v>45476.56679398148</v>
+      <c r="F107" s="24" t="n">
+        <v>45476.58997685185</v>
       </c>
     </row>
     <row r="108">
@@ -3853,8 +3854,8 @@
       <c r="E108" t="n">
         <v>0</v>
       </c>
-      <c r="F108" s="23" t="n">
-        <v>45476.56679398148</v>
+      <c r="F108" s="24" t="n">
+        <v>45476.58997685185</v>
       </c>
     </row>
     <row r="109">
@@ -3879,8 +3880,8 @@
       <c r="E109" t="n">
         <v>0</v>
       </c>
-      <c r="F109" s="23" t="n">
-        <v>45476.56679398148</v>
+      <c r="F109" s="24" t="n">
+        <v>45476.58997685185</v>
       </c>
     </row>
     <row r="110">
@@ -3905,8 +3906,8 @@
       <c r="E110" t="n">
         <v>0</v>
       </c>
-      <c r="F110" s="23" t="n">
-        <v>45476.56679398148</v>
+      <c r="F110" s="24" t="n">
+        <v>45476.58997685185</v>
       </c>
     </row>
     <row r="111">
@@ -3931,8 +3932,8 @@
       <c r="E111" t="n">
         <v>0</v>
       </c>
-      <c r="F111" s="23" t="n">
-        <v>45476.56679398148</v>
+      <c r="F111" s="24" t="n">
+        <v>45476.58997685185</v>
       </c>
     </row>
     <row r="112">
@@ -3957,8 +3958,8 @@
       <c r="E112" t="n">
         <v>0</v>
       </c>
-      <c r="F112" s="23" t="n">
-        <v>45476.56679398148</v>
+      <c r="F112" s="24" t="n">
+        <v>45476.58997685185</v>
       </c>
     </row>
     <row r="113">
@@ -3983,8 +3984,8 @@
       <c r="E113" t="n">
         <v>0</v>
       </c>
-      <c r="F113" s="23" t="n">
-        <v>45476.56679398148</v>
+      <c r="F113" s="24" t="n">
+        <v>45476.58997685185</v>
       </c>
     </row>
     <row r="114">
@@ -4009,8 +4010,8 @@
       <c r="E114" t="n">
         <v>0</v>
       </c>
-      <c r="F114" s="23" t="n">
-        <v>45476.56679398148</v>
+      <c r="F114" s="24" t="n">
+        <v>45476.58997685185</v>
       </c>
     </row>
     <row r="115">
@@ -4035,8 +4036,8 @@
       <c r="E115" t="n">
         <v>0</v>
       </c>
-      <c r="F115" s="23" t="n">
-        <v>45476.56679398148</v>
+      <c r="F115" s="24" t="n">
+        <v>45476.58997685185</v>
       </c>
     </row>
     <row r="116">
@@ -4061,8 +4062,8 @@
       <c r="E116" t="n">
         <v>0</v>
       </c>
-      <c r="F116" s="23" t="n">
-        <v>45476.56679398148</v>
+      <c r="F116" s="24" t="n">
+        <v>45476.58997685185</v>
       </c>
     </row>
     <row r="117">
@@ -4087,8 +4088,8 @@
       <c r="E117" t="n">
         <v>0</v>
       </c>
-      <c r="F117" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F117" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="118">
@@ -4113,8 +4114,8 @@
       <c r="E118" t="n">
         <v>0</v>
       </c>
-      <c r="F118" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F118" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="119">
@@ -4139,8 +4140,8 @@
       <c r="E119" t="n">
         <v>0</v>
       </c>
-      <c r="F119" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F119" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="120">
@@ -4165,8 +4166,8 @@
       <c r="E120" t="n">
         <v>0</v>
       </c>
-      <c r="F120" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F120" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="121">
@@ -4191,8 +4192,8 @@
       <c r="E121" t="n">
         <v>0</v>
       </c>
-      <c r="F121" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F121" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="122">
@@ -4217,8 +4218,8 @@
       <c r="E122" t="n">
         <v>0</v>
       </c>
-      <c r="F122" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F122" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="123">
@@ -4243,8 +4244,8 @@
       <c r="E123" t="n">
         <v>0</v>
       </c>
-      <c r="F123" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F123" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="124">
@@ -4269,8 +4270,8 @@
       <c r="E124" t="n">
         <v>0</v>
       </c>
-      <c r="F124" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F124" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="125">
@@ -4295,8 +4296,8 @@
       <c r="E125" t="n">
         <v>0</v>
       </c>
-      <c r="F125" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F125" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="126">
@@ -4321,8 +4322,8 @@
       <c r="E126" t="n">
         <v>0</v>
       </c>
-      <c r="F126" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F126" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="127">
@@ -4347,8 +4348,8 @@
       <c r="E127" t="n">
         <v>0</v>
       </c>
-      <c r="F127" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F127" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="128">
@@ -4373,8 +4374,8 @@
       <c r="E128" t="n">
         <v>0</v>
       </c>
-      <c r="F128" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F128" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="129">
@@ -4399,8 +4400,8 @@
       <c r="E129" t="n">
         <v>0</v>
       </c>
-      <c r="F129" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F129" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="130">
@@ -4425,8 +4426,8 @@
       <c r="E130" t="n">
         <v>0</v>
       </c>
-      <c r="F130" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F130" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="131">
@@ -4451,8 +4452,8 @@
       <c r="E131" t="n">
         <v>0</v>
       </c>
-      <c r="F131" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F131" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="132">
@@ -4477,8 +4478,8 @@
       <c r="E132" t="n">
         <v>0</v>
       </c>
-      <c r="F132" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F132" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="133">
@@ -4503,8 +4504,8 @@
       <c r="E133" t="n">
         <v>0</v>
       </c>
-      <c r="F133" s="23" t="n">
-        <v>45476.56680555556</v>
+      <c r="F133" s="24" t="n">
+        <v>45476.58998842593</v>
       </c>
     </row>
     <row r="134">
@@ -4529,8 +4530,8 @@
       <c r="E134" t="n">
         <v>0</v>
       </c>
-      <c r="F134" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F134" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="135">
@@ -4555,8 +4556,8 @@
       <c r="E135" t="n">
         <v>0</v>
       </c>
-      <c r="F135" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F135" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="136">
@@ -4581,8 +4582,8 @@
       <c r="E136" t="n">
         <v>0</v>
       </c>
-      <c r="F136" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F136" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="137">
@@ -4607,8 +4608,8 @@
       <c r="E137" t="n">
         <v>0</v>
       </c>
-      <c r="F137" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F137" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="138">
@@ -4633,8 +4634,8 @@
       <c r="E138" t="n">
         <v>0</v>
       </c>
-      <c r="F138" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F138" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="139">
@@ -4659,8 +4660,8 @@
       <c r="E139" t="n">
         <v>0</v>
       </c>
-      <c r="F139" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F139" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="140">
@@ -4685,8 +4686,8 @@
       <c r="E140" t="n">
         <v>0</v>
       </c>
-      <c r="F140" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F140" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="141">
@@ -4711,8 +4712,8 @@
       <c r="E141" t="n">
         <v>0</v>
       </c>
-      <c r="F141" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F141" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="142">
@@ -4737,8 +4738,8 @@
       <c r="E142" t="n">
         <v>0</v>
       </c>
-      <c r="F142" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F142" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="143">
@@ -4763,8 +4764,8 @@
       <c r="E143" t="n">
         <v>0</v>
       </c>
-      <c r="F143" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F143" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="144">
@@ -4789,8 +4790,8 @@
       <c r="E144" t="n">
         <v>0</v>
       </c>
-      <c r="F144" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F144" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="145">
@@ -4815,8 +4816,8 @@
       <c r="E145" t="n">
         <v>0</v>
       </c>
-      <c r="F145" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F145" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="146">
@@ -4841,8 +4842,8 @@
       <c r="E146" t="n">
         <v>0</v>
       </c>
-      <c r="F146" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F146" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="147">
@@ -4867,8 +4868,8 @@
       <c r="E147" t="n">
         <v>0</v>
       </c>
-      <c r="F147" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F147" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="148">
@@ -4893,8 +4894,8 @@
       <c r="E148" t="n">
         <v>0</v>
       </c>
-      <c r="F148" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F148" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="149">
@@ -4919,8 +4920,8 @@
       <c r="E149" t="n">
         <v>0</v>
       </c>
-      <c r="F149" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F149" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="150">
@@ -4945,8 +4946,8 @@
       <c r="E150" t="n">
         <v>0</v>
       </c>
-      <c r="F150" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F150" s="24" t="n">
+        <v>45476.59</v>
       </c>
     </row>
     <row r="151">
@@ -4971,8 +4972,8 @@
       <c r="E151" t="n">
         <v>0</v>
       </c>
-      <c r="F151" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F151" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="152">
@@ -4997,8 +4998,8 @@
       <c r="E152" t="n">
         <v>0</v>
       </c>
-      <c r="F152" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F152" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="153">
@@ -5023,8 +5024,8 @@
       <c r="E153" t="n">
         <v>0</v>
       </c>
-      <c r="F153" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F153" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="154">
@@ -5049,8 +5050,8 @@
       <c r="E154" t="n">
         <v>0</v>
       </c>
-      <c r="F154" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F154" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="155">
@@ -5075,8 +5076,8 @@
       <c r="E155" t="n">
         <v>0</v>
       </c>
-      <c r="F155" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F155" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="156">
@@ -5101,8 +5102,8 @@
       <c r="E156" t="n">
         <v>0</v>
       </c>
-      <c r="F156" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F156" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="157">
@@ -5127,8 +5128,8 @@
       <c r="E157" t="n">
         <v>0</v>
       </c>
-      <c r="F157" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F157" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="158">
@@ -5153,8 +5154,8 @@
       <c r="E158" t="n">
         <v>0</v>
       </c>
-      <c r="F158" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F158" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="159">
@@ -5179,8 +5180,8 @@
       <c r="E159" t="n">
         <v>0</v>
       </c>
-      <c r="F159" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F159" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="160">
@@ -5205,8 +5206,8 @@
       <c r="E160" t="n">
         <v>0</v>
       </c>
-      <c r="F160" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F160" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="161">
@@ -5231,8 +5232,8 @@
       <c r="E161" t="n">
         <v>0</v>
       </c>
-      <c r="F161" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F161" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="162">
@@ -5257,8 +5258,8 @@
       <c r="E162" t="n">
         <v>0</v>
       </c>
-      <c r="F162" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F162" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="163">
@@ -5283,8 +5284,8 @@
       <c r="E163" t="n">
         <v>0</v>
       </c>
-      <c r="F163" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F163" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="164">
@@ -5309,8 +5310,8 @@
       <c r="E164" t="n">
         <v>0</v>
       </c>
-      <c r="F164" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F164" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="165">
@@ -5335,8 +5336,8 @@
       <c r="E165" t="n">
         <v>0</v>
       </c>
-      <c r="F165" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F165" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="166">
@@ -5361,8 +5362,8 @@
       <c r="E166" t="n">
         <v>0</v>
       </c>
-      <c r="F166" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F166" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="167">
@@ -5387,8 +5388,8 @@
       <c r="E167" t="n">
         <v>0</v>
       </c>
-      <c r="F167" s="23" t="n">
-        <v>45476.56681712963</v>
+      <c r="F167" s="24" t="n">
+        <v>45476.59001157407</v>
       </c>
     </row>
     <row r="168">
@@ -5409,8 +5410,8 @@
       <c r="E168" t="n">
         <v>0</v>
       </c>
-      <c r="F168" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F168" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="169">
@@ -5435,8 +5436,8 @@
       <c r="E169" t="n">
         <v>0</v>
       </c>
-      <c r="F169" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F169" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="170">
@@ -5461,8 +5462,8 @@
       <c r="E170" t="n">
         <v>0</v>
       </c>
-      <c r="F170" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F170" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="171">
@@ -5487,8 +5488,8 @@
       <c r="E171" t="n">
         <v>0</v>
       </c>
-      <c r="F171" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F171" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="172">
@@ -5513,8 +5514,8 @@
       <c r="E172" t="n">
         <v>0</v>
       </c>
-      <c r="F172" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F172" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="173">
@@ -5539,8 +5540,8 @@
       <c r="E173" t="n">
         <v>0</v>
       </c>
-      <c r="F173" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F173" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="174">
@@ -5565,8 +5566,8 @@
       <c r="E174" t="n">
         <v>0</v>
       </c>
-      <c r="F174" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F174" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="175">
@@ -5591,8 +5592,8 @@
       <c r="E175" t="n">
         <v>0</v>
       </c>
-      <c r="F175" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F175" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="176">
@@ -5617,8 +5618,8 @@
       <c r="E176" t="n">
         <v>0</v>
       </c>
-      <c r="F176" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F176" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="177">
@@ -5643,8 +5644,8 @@
       <c r="E177" t="n">
         <v>0</v>
       </c>
-      <c r="F177" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F177" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="178">
@@ -5669,8 +5670,8 @@
       <c r="E178" t="n">
         <v>0</v>
       </c>
-      <c r="F178" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F178" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="179">
@@ -5695,8 +5696,8 @@
       <c r="E179" t="n">
         <v>0</v>
       </c>
-      <c r="F179" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F179" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="180">
@@ -5721,8 +5722,8 @@
       <c r="E180" t="n">
         <v>0</v>
       </c>
-      <c r="F180" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F180" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="181">
@@ -5747,8 +5748,8 @@
       <c r="E181" t="n">
         <v>0</v>
       </c>
-      <c r="F181" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F181" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="182">
@@ -5773,8 +5774,8 @@
       <c r="E182" t="n">
         <v>0</v>
       </c>
-      <c r="F182" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F182" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="183">
@@ -5799,8 +5800,8 @@
       <c r="E183" t="n">
         <v>0</v>
       </c>
-      <c r="F183" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F183" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="184">
@@ -5825,8 +5826,8 @@
       <c r="E184" t="n">
         <v>0</v>
       </c>
-      <c r="F184" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F184" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="185">
@@ -5851,8 +5852,8 @@
       <c r="E185" t="n">
         <v>0</v>
       </c>
-      <c r="F185" s="23" t="n">
-        <v>45476.5668287037</v>
+      <c r="F185" s="24" t="n">
+        <v>45476.59002314815</v>
       </c>
     </row>
     <row r="186">
@@ -5877,8 +5878,8 @@
       <c r="E186" t="n">
         <v>0</v>
       </c>
-      <c r="F186" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F186" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="187">
@@ -5903,8 +5904,8 @@
       <c r="E187" t="n">
         <v>0</v>
       </c>
-      <c r="F187" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F187" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="188">
@@ -5929,8 +5930,8 @@
       <c r="E188" t="n">
         <v>0</v>
       </c>
-      <c r="F188" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F188" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="189">
@@ -5955,8 +5956,8 @@
       <c r="E189" t="n">
         <v>0</v>
       </c>
-      <c r="F189" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F189" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="190">
@@ -5981,8 +5982,8 @@
       <c r="E190" t="n">
         <v>0</v>
       </c>
-      <c r="F190" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F190" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="191">
@@ -6007,8 +6008,8 @@
       <c r="E191" t="n">
         <v>0</v>
       </c>
-      <c r="F191" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F191" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="192">
@@ -6033,8 +6034,8 @@
       <c r="E192" t="n">
         <v>0</v>
       </c>
-      <c r="F192" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F192" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="193">
@@ -6059,8 +6060,8 @@
       <c r="E193" t="n">
         <v>0</v>
       </c>
-      <c r="F193" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F193" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="194">
@@ -6085,8 +6086,8 @@
       <c r="E194" t="n">
         <v>0</v>
       </c>
-      <c r="F194" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F194" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="195">
@@ -6111,8 +6112,8 @@
       <c r="E195" t="n">
         <v>0</v>
       </c>
-      <c r="F195" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F195" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="196">
@@ -6137,8 +6138,8 @@
       <c r="E196" t="n">
         <v>0</v>
       </c>
-      <c r="F196" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F196" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="197">
@@ -6163,8 +6164,8 @@
       <c r="E197" t="n">
         <v>0</v>
       </c>
-      <c r="F197" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F197" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="198">
@@ -6189,8 +6190,8 @@
       <c r="E198" t="n">
         <v>0</v>
       </c>
-      <c r="F198" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F198" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="199">
@@ -6215,8 +6216,8 @@
       <c r="E199" t="n">
         <v>0</v>
       </c>
-      <c r="F199" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F199" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="200">
@@ -6241,8 +6242,8 @@
       <c r="E200" t="n">
         <v>0</v>
       </c>
-      <c r="F200" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F200" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="201">
@@ -6267,8 +6268,8 @@
       <c r="E201" t="n">
         <v>0</v>
       </c>
-      <c r="F201" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F201" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="202">
@@ -6293,8 +6294,8 @@
       <c r="E202" t="n">
         <v>0</v>
       </c>
-      <c r="F202" s="23" t="n">
-        <v>45476.56684027778</v>
+      <c r="F202" s="24" t="n">
+        <v>45476.5900462963</v>
       </c>
     </row>
     <row r="203">
@@ -6319,8 +6320,8 @@
       <c r="E203" t="n">
         <v>0</v>
       </c>
-      <c r="F203" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F203" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="204">
@@ -6345,8 +6346,8 @@
       <c r="E204" t="n">
         <v>0</v>
       </c>
-      <c r="F204" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F204" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="205">
@@ -6371,8 +6372,8 @@
       <c r="E205" t="n">
         <v>0</v>
       </c>
-      <c r="F205" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F205" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="206">
@@ -6397,8 +6398,8 @@
       <c r="E206" t="n">
         <v>0</v>
       </c>
-      <c r="F206" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F206" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="207">
@@ -6423,8 +6424,8 @@
       <c r="E207" t="n">
         <v>0</v>
       </c>
-      <c r="F207" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F207" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="208">
@@ -6449,8 +6450,8 @@
       <c r="E208" t="n">
         <v>0</v>
       </c>
-      <c r="F208" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F208" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="209">
@@ -6475,8 +6476,8 @@
       <c r="E209" t="n">
         <v>0</v>
       </c>
-      <c r="F209" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F209" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="210">
@@ -6501,8 +6502,8 @@
       <c r="E210" t="n">
         <v>0</v>
       </c>
-      <c r="F210" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F210" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="211">
@@ -6527,8 +6528,8 @@
       <c r="E211" t="n">
         <v>0</v>
       </c>
-      <c r="F211" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F211" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="212">
@@ -6553,8 +6554,8 @@
       <c r="E212" t="n">
         <v>0</v>
       </c>
-      <c r="F212" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F212" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="213">
@@ -6579,8 +6580,8 @@
       <c r="E213" t="n">
         <v>0</v>
       </c>
-      <c r="F213" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F213" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="214">
@@ -6605,8 +6606,8 @@
       <c r="E214" t="n">
         <v>0</v>
       </c>
-      <c r="F214" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F214" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="215">
@@ -6631,8 +6632,8 @@
       <c r="E215" t="n">
         <v>0</v>
       </c>
-      <c r="F215" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F215" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="216">
@@ -6657,8 +6658,8 @@
       <c r="E216" t="n">
         <v>0</v>
       </c>
-      <c r="F216" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F216" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="217">
@@ -6683,8 +6684,8 @@
       <c r="E217" t="n">
         <v>0</v>
       </c>
-      <c r="F217" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F217" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="218">
@@ -6709,8 +6710,8 @@
       <c r="E218" t="n">
         <v>0</v>
       </c>
-      <c r="F218" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F218" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="219">
@@ -6735,8 +6736,8 @@
       <c r="E219" t="n">
         <v>0</v>
       </c>
-      <c r="F219" s="23" t="n">
-        <v>45476.56685185185</v>
+      <c r="F219" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="220">
@@ -6761,8 +6762,8 @@
       <c r="E220" t="n">
         <v>0</v>
       </c>
-      <c r="F220" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F220" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="221">
@@ -6787,8 +6788,8 @@
       <c r="E221" t="n">
         <v>0</v>
       </c>
-      <c r="F221" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F221" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="222">
@@ -6813,8 +6814,8 @@
       <c r="E222" t="n">
         <v>0</v>
       </c>
-      <c r="F222" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F222" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="223">
@@ -6839,8 +6840,8 @@
       <c r="E223" t="n">
         <v>0</v>
       </c>
-      <c r="F223" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F223" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="224">
@@ -6865,8 +6866,8 @@
       <c r="E224" t="n">
         <v>0</v>
       </c>
-      <c r="F224" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F224" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="225">
@@ -6891,8 +6892,8 @@
       <c r="E225" t="n">
         <v>0</v>
       </c>
-      <c r="F225" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F225" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="226">
@@ -6917,8 +6918,8 @@
       <c r="E226" t="n">
         <v>0</v>
       </c>
-      <c r="F226" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F226" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="227">
@@ -6943,8 +6944,8 @@
       <c r="E227" t="n">
         <v>0</v>
       </c>
-      <c r="F227" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F227" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="228">
@@ -6969,8 +6970,8 @@
       <c r="E228" t="n">
         <v>0</v>
       </c>
-      <c r="F228" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F228" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="229">
@@ -6995,8 +6996,8 @@
       <c r="E229" t="n">
         <v>0</v>
       </c>
-      <c r="F229" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F229" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="230">
@@ -7021,8 +7022,8 @@
       <c r="E230" t="n">
         <v>0</v>
       </c>
-      <c r="F230" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F230" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="231">
@@ -7047,8 +7048,8 @@
       <c r="E231" t="n">
         <v>0</v>
       </c>
-      <c r="F231" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F231" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="232">
@@ -7073,8 +7074,8 @@
       <c r="E232" t="n">
         <v>0</v>
       </c>
-      <c r="F232" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F232" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="233">
@@ -7099,8 +7100,8 @@
       <c r="E233" t="n">
         <v>0</v>
       </c>
-      <c r="F233" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F233" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="234">
@@ -7125,8 +7126,8 @@
       <c r="E234" t="n">
         <v>0</v>
       </c>
-      <c r="F234" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F234" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="235">
@@ -7151,8 +7152,8 @@
       <c r="E235" t="n">
         <v>0</v>
       </c>
-      <c r="F235" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F235" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="236">
@@ -7177,8 +7178,8 @@
       <c r="E236" t="n">
         <v>0</v>
       </c>
-      <c r="F236" s="23" t="n">
-        <v>45476.566875</v>
+      <c r="F236" s="24" t="n">
+        <v>45476.59005787037</v>
       </c>
     </row>
     <row r="237">
@@ -7203,8 +7204,8 @@
       <c r="E237" t="n">
         <v>0</v>
       </c>
-      <c r="F237" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F237" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="238">
@@ -7229,8 +7230,8 @@
       <c r="E238" t="n">
         <v>0</v>
       </c>
-      <c r="F238" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F238" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="239">
@@ -7255,8 +7256,8 @@
       <c r="E239" t="n">
         <v>0</v>
       </c>
-      <c r="F239" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F239" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="240">
@@ -7281,8 +7282,8 @@
       <c r="E240" t="n">
         <v>0</v>
       </c>
-      <c r="F240" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F240" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="241">
@@ -7307,8 +7308,8 @@
       <c r="E241" t="n">
         <v>0</v>
       </c>
-      <c r="F241" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F241" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="242">
@@ -7333,8 +7334,8 @@
       <c r="E242" t="n">
         <v>0</v>
       </c>
-      <c r="F242" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F242" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="243">
@@ -7359,8 +7360,8 @@
       <c r="E243" t="n">
         <v>0</v>
       </c>
-      <c r="F243" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F243" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="244">
@@ -7385,8 +7386,8 @@
       <c r="E244" t="n">
         <v>0</v>
       </c>
-      <c r="F244" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F244" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="245">
@@ -7411,8 +7412,8 @@
       <c r="E245" t="n">
         <v>0</v>
       </c>
-      <c r="F245" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F245" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="246">
@@ -7437,8 +7438,8 @@
       <c r="E246" t="n">
         <v>0</v>
       </c>
-      <c r="F246" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F246" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="247">
@@ -7463,8 +7464,8 @@
       <c r="E247" t="n">
         <v>0</v>
       </c>
-      <c r="F247" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F247" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="248">
@@ -7489,8 +7490,8 @@
       <c r="E248" t="n">
         <v>0</v>
       </c>
-      <c r="F248" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F248" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="249">
@@ -7515,8 +7516,8 @@
       <c r="E249" t="n">
         <v>0</v>
       </c>
-      <c r="F249" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F249" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="250">
@@ -7541,8 +7542,8 @@
       <c r="E250" t="n">
         <v>0</v>
       </c>
-      <c r="F250" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F250" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="251">
@@ -7567,8 +7568,8 @@
       <c r="E251" t="n">
         <v>0</v>
       </c>
-      <c r="F251" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F251" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="252">
@@ -7593,8 +7594,8 @@
       <c r="E252" t="n">
         <v>0</v>
       </c>
-      <c r="F252" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F252" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="253">
@@ -7619,8 +7620,8 @@
       <c r="E253" t="n">
         <v>0</v>
       </c>
-      <c r="F253" s="23" t="n">
-        <v>45476.56688657407</v>
+      <c r="F253" s="24" t="n">
+        <v>45476.59008101852</v>
       </c>
     </row>
     <row r="254">
@@ -7645,8 +7646,8 @@
       <c r="E254" t="n">
         <v>0</v>
       </c>
-      <c r="F254" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F254" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="255">
@@ -7671,8 +7672,8 @@
       <c r="E255" t="n">
         <v>0</v>
       </c>
-      <c r="F255" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F255" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="256">
@@ -7697,8 +7698,8 @@
       <c r="E256" t="n">
         <v>0</v>
       </c>
-      <c r="F256" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F256" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="257">
@@ -7723,8 +7724,8 @@
       <c r="E257" t="n">
         <v>0</v>
       </c>
-      <c r="F257" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F257" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="258">
@@ -7749,8 +7750,8 @@
       <c r="E258" t="n">
         <v>0</v>
       </c>
-      <c r="F258" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F258" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="259">
@@ -7775,8 +7776,8 @@
       <c r="E259" t="n">
         <v>0</v>
       </c>
-      <c r="F259" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F259" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="260">
@@ -7801,8 +7802,8 @@
       <c r="E260" t="n">
         <v>0</v>
       </c>
-      <c r="F260" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F260" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="261">
@@ -7827,8 +7828,8 @@
       <c r="E261" t="n">
         <v>0</v>
       </c>
-      <c r="F261" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F261" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="262">
@@ -7853,8 +7854,8 @@
       <c r="E262" t="n">
         <v>0</v>
       </c>
-      <c r="F262" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F262" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="263">
@@ -7879,8 +7880,8 @@
       <c r="E263" t="n">
         <v>0</v>
       </c>
-      <c r="F263" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F263" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="264">
@@ -7905,8 +7906,8 @@
       <c r="E264" t="n">
         <v>0</v>
       </c>
-      <c r="F264" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F264" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="265">
@@ -7931,8 +7932,8 @@
       <c r="E265" t="n">
         <v>0</v>
       </c>
-      <c r="F265" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F265" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="266">
@@ -7957,8 +7958,8 @@
       <c r="E266" t="n">
         <v>0</v>
       </c>
-      <c r="F266" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F266" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="267">
@@ -7983,8 +7984,8 @@
       <c r="E267" t="n">
         <v>0</v>
       </c>
-      <c r="F267" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F267" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="268">
@@ -8009,8 +8010,8 @@
       <c r="E268" t="n">
         <v>0</v>
       </c>
-      <c r="F268" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F268" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="269">
@@ -8035,8 +8036,8 @@
       <c r="E269" t="n">
         <v>0</v>
       </c>
-      <c r="F269" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F269" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="270">
@@ -8061,8 +8062,8 @@
       <c r="E270" t="n">
         <v>0</v>
       </c>
-      <c r="F270" s="23" t="n">
-        <v>45476.56690972222</v>
+      <c r="F270" s="24" t="n">
+        <v>45476.5900925926</v>
       </c>
     </row>
     <row r="271">
@@ -8087,8 +8088,8 @@
       <c r="E271" t="n">
         <v>0</v>
       </c>
-      <c r="F271" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F271" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="272">
@@ -8113,8 +8114,8 @@
       <c r="E272" t="n">
         <v>0</v>
       </c>
-      <c r="F272" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F272" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="273">
@@ -8139,8 +8140,8 @@
       <c r="E273" t="n">
         <v>0</v>
       </c>
-      <c r="F273" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F273" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="274">
@@ -8165,8 +8166,8 @@
       <c r="E274" t="n">
         <v>0</v>
       </c>
-      <c r="F274" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F274" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="275">
@@ -8191,8 +8192,8 @@
       <c r="E275" t="n">
         <v>0</v>
       </c>
-      <c r="F275" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F275" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="276">
@@ -8217,8 +8218,8 @@
       <c r="E276" t="n">
         <v>0</v>
       </c>
-      <c r="F276" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F276" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="277">
@@ -8243,8 +8244,8 @@
       <c r="E277" t="n">
         <v>0</v>
       </c>
-      <c r="F277" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F277" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="278">
@@ -8269,8 +8270,8 @@
       <c r="E278" t="n">
         <v>0</v>
       </c>
-      <c r="F278" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F278" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="279">
@@ -8295,8 +8296,8 @@
       <c r="E279" t="n">
         <v>0</v>
       </c>
-      <c r="F279" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F279" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="280">
@@ -8321,8 +8322,8 @@
       <c r="E280" t="n">
         <v>0</v>
       </c>
-      <c r="F280" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F280" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="281">
@@ -8347,8 +8348,8 @@
       <c r="E281" t="n">
         <v>0</v>
       </c>
-      <c r="F281" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F281" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="282">
@@ -8373,8 +8374,8 @@
       <c r="E282" t="n">
         <v>0</v>
       </c>
-      <c r="F282" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F282" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="283">
@@ -8399,8 +8400,8 @@
       <c r="E283" t="n">
         <v>0</v>
       </c>
-      <c r="F283" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F283" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="284">
@@ -8425,8 +8426,8 @@
       <c r="E284" t="n">
         <v>0</v>
       </c>
-      <c r="F284" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F284" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="285">
@@ -8451,8 +8452,8 @@
       <c r="E285" t="n">
         <v>0</v>
       </c>
-      <c r="F285" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F285" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="286">
@@ -8477,8 +8478,8 @@
       <c r="E286" t="n">
         <v>0</v>
       </c>
-      <c r="F286" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F286" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="287">
@@ -8503,8 +8504,8 @@
       <c r="E287" t="n">
         <v>0</v>
       </c>
-      <c r="F287" s="23" t="n">
-        <v>45476.5669212963</v>
+      <c r="F287" s="24" t="n">
+        <v>45476.59010416667</v>
       </c>
     </row>
     <row r="288">
@@ -8529,8 +8530,8 @@
       <c r="E288" t="n">
         <v>0</v>
       </c>
-      <c r="F288" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F288" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="289">
@@ -8555,8 +8556,8 @@
       <c r="E289" t="n">
         <v>0</v>
       </c>
-      <c r="F289" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F289" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="290">
@@ -8581,8 +8582,8 @@
       <c r="E290" t="n">
         <v>0</v>
       </c>
-      <c r="F290" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F290" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="291">
@@ -8607,8 +8608,8 @@
       <c r="E291" t="n">
         <v>0</v>
       </c>
-      <c r="F291" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F291" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="292">
@@ -8633,8 +8634,8 @@
       <c r="E292" t="n">
         <v>0</v>
       </c>
-      <c r="F292" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F292" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="293">
@@ -8659,8 +8660,8 @@
       <c r="E293" t="n">
         <v>0</v>
       </c>
-      <c r="F293" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F293" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="294">
@@ -8685,8 +8686,8 @@
       <c r="E294" t="n">
         <v>0</v>
       </c>
-      <c r="F294" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F294" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="295">
@@ -8711,8 +8712,8 @@
       <c r="E295" t="n">
         <v>0</v>
       </c>
-      <c r="F295" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F295" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="296">
@@ -8737,8 +8738,8 @@
       <c r="E296" t="n">
         <v>0</v>
       </c>
-      <c r="F296" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F296" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="297">
@@ -8763,8 +8764,8 @@
       <c r="E297" t="n">
         <v>0</v>
       </c>
-      <c r="F297" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F297" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="298">
@@ -8789,8 +8790,8 @@
       <c r="E298" t="n">
         <v>0</v>
       </c>
-      <c r="F298" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F298" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="299">
@@ -8815,8 +8816,8 @@
       <c r="E299" t="n">
         <v>0</v>
       </c>
-      <c r="F299" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F299" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="300">
@@ -8841,8 +8842,8 @@
       <c r="E300" t="n">
         <v>0</v>
       </c>
-      <c r="F300" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F300" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="301">
@@ -8867,8 +8868,8 @@
       <c r="E301" t="n">
         <v>0</v>
       </c>
-      <c r="F301" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F301" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="302">
@@ -8893,8 +8894,8 @@
       <c r="E302" t="n">
         <v>0</v>
       </c>
-      <c r="F302" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F302" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="303">
@@ -8919,8 +8920,8 @@
       <c r="E303" t="n">
         <v>0</v>
       </c>
-      <c r="F303" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F303" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="304">
@@ -8945,8 +8946,8 @@
       <c r="E304" t="n">
         <v>0</v>
       </c>
-      <c r="F304" s="23" t="n">
-        <v>45476.56693287037</v>
+      <c r="F304" s="24" t="n">
+        <v>45476.59012731481</v>
       </c>
     </row>
     <row r="305">
@@ -8971,8 +8972,8 @@
       <c r="E305" t="n">
         <v>0</v>
       </c>
-      <c r="F305" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F305" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="306">
@@ -8997,8 +8998,8 @@
       <c r="E306" t="n">
         <v>0</v>
       </c>
-      <c r="F306" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F306" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="307">
@@ -9023,8 +9024,8 @@
       <c r="E307" t="n">
         <v>0</v>
       </c>
-      <c r="F307" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F307" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="308">
@@ -9049,8 +9050,8 @@
       <c r="E308" t="n">
         <v>0</v>
       </c>
-      <c r="F308" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F308" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="309">
@@ -9075,8 +9076,8 @@
       <c r="E309" t="n">
         <v>0</v>
       </c>
-      <c r="F309" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F309" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="310">
@@ -9101,8 +9102,8 @@
       <c r="E310" t="n">
         <v>0</v>
       </c>
-      <c r="F310" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F310" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="311">
@@ -9127,8 +9128,8 @@
       <c r="E311" t="n">
         <v>0</v>
       </c>
-      <c r="F311" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F311" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="312">
@@ -9153,8 +9154,8 @@
       <c r="E312" t="n">
         <v>0</v>
       </c>
-      <c r="F312" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F312" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="313">
@@ -9179,8 +9180,8 @@
       <c r="E313" t="n">
         <v>0</v>
       </c>
-      <c r="F313" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F313" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="314">
@@ -9205,8 +9206,8 @@
       <c r="E314" t="n">
         <v>0</v>
       </c>
-      <c r="F314" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F314" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="315">
@@ -9231,8 +9232,8 @@
       <c r="E315" t="n">
         <v>0</v>
       </c>
-      <c r="F315" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F315" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="316">
@@ -9257,8 +9258,8 @@
       <c r="E316" t="n">
         <v>0</v>
       </c>
-      <c r="F316" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F316" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="317">
@@ -9283,8 +9284,8 @@
       <c r="E317" t="n">
         <v>0</v>
       </c>
-      <c r="F317" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F317" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="318">
@@ -9309,8 +9310,8 @@
       <c r="E318" t="n">
         <v>0</v>
       </c>
-      <c r="F318" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F318" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="319">
@@ -9335,8 +9336,8 @@
       <c r="E319" t="n">
         <v>0</v>
       </c>
-      <c r="F319" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F319" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="320">
@@ -9361,8 +9362,8 @@
       <c r="E320" t="n">
         <v>0</v>
       </c>
-      <c r="F320" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F320" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="321">
@@ -9387,8 +9388,8 @@
       <c r="E321" t="n">
         <v>0</v>
       </c>
-      <c r="F321" s="23" t="n">
-        <v>45476.56694444444</v>
+      <c r="F321" s="24" t="n">
+        <v>45476.59013888889</v>
       </c>
     </row>
     <row r="322">
@@ -9409,8 +9410,8 @@
       <c r="E322" t="n">
         <v>0</v>
       </c>
-      <c r="F322" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F322" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="323">
@@ -9435,8 +9436,8 @@
       <c r="E323" t="n">
         <v>0</v>
       </c>
-      <c r="F323" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F323" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="324">
@@ -9461,8 +9462,8 @@
       <c r="E324" t="n">
         <v>0</v>
       </c>
-      <c r="F324" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F324" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="325">
@@ -9487,8 +9488,8 @@
       <c r="E325" t="n">
         <v>0</v>
       </c>
-      <c r="F325" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F325" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="326">
@@ -9513,8 +9514,8 @@
       <c r="E326" t="n">
         <v>0</v>
       </c>
-      <c r="F326" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F326" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="327">
@@ -9539,8 +9540,8 @@
       <c r="E327" t="n">
         <v>0</v>
       </c>
-      <c r="F327" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F327" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="328">
@@ -9565,8 +9566,8 @@
       <c r="E328" t="n">
         <v>0</v>
       </c>
-      <c r="F328" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F328" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="329">
@@ -9591,8 +9592,8 @@
       <c r="E329" t="n">
         <v>0</v>
       </c>
-      <c r="F329" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F329" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="330">
@@ -9617,8 +9618,8 @@
       <c r="E330" t="n">
         <v>0</v>
       </c>
-      <c r="F330" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F330" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="331">
@@ -9643,8 +9644,8 @@
       <c r="E331" t="n">
         <v>0</v>
       </c>
-      <c r="F331" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F331" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="332">
@@ -9669,8 +9670,8 @@
       <c r="E332" t="n">
         <v>0</v>
       </c>
-      <c r="F332" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F332" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="333">
@@ -9695,8 +9696,8 @@
       <c r="E333" t="n">
         <v>0</v>
       </c>
-      <c r="F333" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F333" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="334">
@@ -9721,8 +9722,8 @@
       <c r="E334" t="n">
         <v>0</v>
       </c>
-      <c r="F334" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F334" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="335">
@@ -9747,8 +9748,8 @@
       <c r="E335" t="n">
         <v>0</v>
       </c>
-      <c r="F335" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F335" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="336">
@@ -9773,8 +9774,8 @@
       <c r="E336" t="n">
         <v>0</v>
       </c>
-      <c r="F336" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F336" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="337">
@@ -9799,8 +9800,8 @@
       <c r="E337" t="n">
         <v>0</v>
       </c>
-      <c r="F337" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F337" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="338">
@@ -9825,8 +9826,8 @@
       <c r="E338" t="n">
         <v>0</v>
       </c>
-      <c r="F338" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F338" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="339">
@@ -9851,8 +9852,8 @@
       <c r="E339" t="n">
         <v>0</v>
       </c>
-      <c r="F339" s="23" t="n">
-        <v>45476.56695601852</v>
+      <c r="F339" s="24" t="n">
+        <v>45476.59015046297</v>
       </c>
     </row>
     <row r="340">
@@ -9877,8 +9878,8 @@
       <c r="E340" t="n">
         <v>0</v>
       </c>
-      <c r="F340" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F340" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="341">
@@ -9903,8 +9904,8 @@
       <c r="E341" t="n">
         <v>0</v>
       </c>
-      <c r="F341" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F341" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="342">
@@ -9929,8 +9930,8 @@
       <c r="E342" t="n">
         <v>0</v>
       </c>
-      <c r="F342" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F342" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="343">
@@ -9955,8 +9956,8 @@
       <c r="E343" t="n">
         <v>0</v>
       </c>
-      <c r="F343" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F343" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="344">
@@ -9981,8 +9982,8 @@
       <c r="E344" t="n">
         <v>0</v>
       </c>
-      <c r="F344" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F344" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="345">
@@ -10007,8 +10008,8 @@
       <c r="E345" t="n">
         <v>0</v>
       </c>
-      <c r="F345" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F345" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="346">
@@ -10033,8 +10034,8 @@
       <c r="E346" t="n">
         <v>0</v>
       </c>
-      <c r="F346" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F346" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="347">
@@ -10059,8 +10060,8 @@
       <c r="E347" t="n">
         <v>0</v>
       </c>
-      <c r="F347" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F347" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="348">
@@ -10085,8 +10086,8 @@
       <c r="E348" t="n">
         <v>0</v>
       </c>
-      <c r="F348" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F348" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="349">
@@ -10111,8 +10112,8 @@
       <c r="E349" t="n">
         <v>0</v>
       </c>
-      <c r="F349" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F349" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="350">
@@ -10137,8 +10138,8 @@
       <c r="E350" t="n">
         <v>0</v>
       </c>
-      <c r="F350" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F350" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="351">
@@ -10163,8 +10164,8 @@
       <c r="E351" t="n">
         <v>0</v>
       </c>
-      <c r="F351" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F351" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="352">
@@ -10189,8 +10190,8 @@
       <c r="E352" t="n">
         <v>0</v>
       </c>
-      <c r="F352" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F352" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="353">
@@ -10215,8 +10216,8 @@
       <c r="E353" t="n">
         <v>0</v>
       </c>
-      <c r="F353" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F353" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="354">
@@ -10241,8 +10242,8 @@
       <c r="E354" t="n">
         <v>0</v>
       </c>
-      <c r="F354" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F354" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="355">
@@ -10267,8 +10268,8 @@
       <c r="E355" t="n">
         <v>0</v>
       </c>
-      <c r="F355" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F355" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="356">
@@ -10293,8 +10294,8 @@
       <c r="E356" t="n">
         <v>0</v>
       </c>
-      <c r="F356" s="23" t="n">
-        <v>45476.56696759259</v>
+      <c r="F356" s="24" t="n">
+        <v>45476.59016203704</v>
       </c>
     </row>
     <row r="357">
@@ -10319,8 +10320,8 @@
       <c r="E357" t="n">
         <v>0</v>
       </c>
-      <c r="F357" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F357" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="358">
@@ -10345,8 +10346,8 @@
       <c r="E358" t="n">
         <v>0</v>
       </c>
-      <c r="F358" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F358" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="359">
@@ -10371,8 +10372,8 @@
       <c r="E359" t="n">
         <v>0</v>
       </c>
-      <c r="F359" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F359" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="360">
@@ -10397,8 +10398,8 @@
       <c r="E360" t="n">
         <v>0</v>
       </c>
-      <c r="F360" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F360" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="361">
@@ -10423,8 +10424,8 @@
       <c r="E361" t="n">
         <v>0</v>
       </c>
-      <c r="F361" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F361" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="362">
@@ -10449,8 +10450,8 @@
       <c r="E362" t="n">
         <v>0</v>
       </c>
-      <c r="F362" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F362" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="363">
@@ -10475,8 +10476,8 @@
       <c r="E363" t="n">
         <v>0</v>
       </c>
-      <c r="F363" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F363" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="364">
@@ -10501,8 +10502,8 @@
       <c r="E364" t="n">
         <v>0</v>
       </c>
-      <c r="F364" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F364" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="365">
@@ -10527,8 +10528,8 @@
       <c r="E365" t="n">
         <v>0</v>
       </c>
-      <c r="F365" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F365" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="366">
@@ -10553,8 +10554,8 @@
       <c r="E366" t="n">
         <v>0</v>
       </c>
-      <c r="F366" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F366" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="367">
@@ -10579,8 +10580,8 @@
       <c r="E367" t="n">
         <v>0</v>
       </c>
-      <c r="F367" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F367" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="368">
@@ -10605,8 +10606,8 @@
       <c r="E368" t="n">
         <v>0</v>
       </c>
-      <c r="F368" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F368" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="369">
@@ -10631,8 +10632,8 @@
       <c r="E369" t="n">
         <v>0</v>
       </c>
-      <c r="F369" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F369" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="370">
@@ -10657,8 +10658,8 @@
       <c r="E370" t="n">
         <v>0</v>
       </c>
-      <c r="F370" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F370" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="371">
@@ -10683,8 +10684,8 @@
       <c r="E371" t="n">
         <v>0</v>
       </c>
-      <c r="F371" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F371" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="372">
@@ -10709,8 +10710,8 @@
       <c r="E372" t="n">
         <v>0</v>
       </c>
-      <c r="F372" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F372" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="373">
@@ -10735,8 +10736,8 @@
       <c r="E373" t="n">
         <v>0</v>
       </c>
-      <c r="F373" s="23" t="n">
-        <v>45476.56699074074</v>
+      <c r="F373" s="24" t="n">
+        <v>45476.59017361111</v>
       </c>
     </row>
     <row r="374">
@@ -10761,8 +10762,8 @@
       <c r="E374" t="n">
         <v>0</v>
       </c>
-      <c r="F374" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F374" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="375">
@@ -10787,8 +10788,8 @@
       <c r="E375" t="n">
         <v>0</v>
       </c>
-      <c r="F375" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F375" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="376">
@@ -10813,8 +10814,8 @@
       <c r="E376" t="n">
         <v>0</v>
       </c>
-      <c r="F376" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F376" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="377">
@@ -10839,8 +10840,8 @@
       <c r="E377" t="n">
         <v>0</v>
       </c>
-      <c r="F377" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F377" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="378">
@@ -10865,8 +10866,8 @@
       <c r="E378" t="n">
         <v>0</v>
       </c>
-      <c r="F378" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F378" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="379">
@@ -10891,8 +10892,8 @@
       <c r="E379" t="n">
         <v>0</v>
       </c>
-      <c r="F379" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F379" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="380">
@@ -10917,8 +10918,8 @@
       <c r="E380" t="n">
         <v>0</v>
       </c>
-      <c r="F380" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F380" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="381">
@@ -10943,8 +10944,8 @@
       <c r="E381" t="n">
         <v>0</v>
       </c>
-      <c r="F381" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F381" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="382">
@@ -10969,8 +10970,8 @@
       <c r="E382" t="n">
         <v>0</v>
       </c>
-      <c r="F382" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F382" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="383">
@@ -10995,8 +10996,8 @@
       <c r="E383" t="n">
         <v>0</v>
       </c>
-      <c r="F383" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F383" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="384">
@@ -11021,8 +11022,8 @@
       <c r="E384" t="n">
         <v>0</v>
       </c>
-      <c r="F384" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F384" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="385">
@@ -11047,8 +11048,8 @@
       <c r="E385" t="n">
         <v>0</v>
       </c>
-      <c r="F385" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F385" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="386">
@@ -11073,8 +11074,8 @@
       <c r="E386" t="n">
         <v>0</v>
       </c>
-      <c r="F386" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F386" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="387">
@@ -11099,8 +11100,8 @@
       <c r="E387" t="n">
         <v>0</v>
       </c>
-      <c r="F387" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F387" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="388">
@@ -11125,8 +11126,8 @@
       <c r="E388" t="n">
         <v>0</v>
       </c>
-      <c r="F388" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F388" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="389">
@@ -11151,8 +11152,8 @@
       <c r="E389" t="n">
         <v>0</v>
       </c>
-      <c r="F389" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F389" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="390">
@@ -11177,8 +11178,8 @@
       <c r="E390" t="n">
         <v>0</v>
       </c>
-      <c r="F390" s="23" t="n">
-        <v>45476.56700231481</v>
+      <c r="F390" s="24" t="n">
+        <v>45476.59018518519</v>
       </c>
     </row>
     <row r="391">
@@ -11203,8 +11204,8 @@
       <c r="E391" t="n">
         <v>0</v>
       </c>
-      <c r="F391" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F391" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="392">
@@ -11229,8 +11230,8 @@
       <c r="E392" t="n">
         <v>0</v>
       </c>
-      <c r="F392" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F392" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="393">
@@ -11255,8 +11256,8 @@
       <c r="E393" t="n">
         <v>0</v>
       </c>
-      <c r="F393" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F393" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="394">
@@ -11281,8 +11282,8 @@
       <c r="E394" t="n">
         <v>0</v>
       </c>
-      <c r="F394" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F394" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="395">
@@ -11307,8 +11308,8 @@
       <c r="E395" t="n">
         <v>0</v>
       </c>
-      <c r="F395" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F395" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="396">
@@ -11333,8 +11334,8 @@
       <c r="E396" t="n">
         <v>0</v>
       </c>
-      <c r="F396" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F396" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="397">
@@ -11359,8 +11360,8 @@
       <c r="E397" t="n">
         <v>0</v>
       </c>
-      <c r="F397" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F397" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="398">
@@ -11385,8 +11386,8 @@
       <c r="E398" t="n">
         <v>0</v>
       </c>
-      <c r="F398" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F398" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="399">
@@ -11411,8 +11412,8 @@
       <c r="E399" t="n">
         <v>0</v>
       </c>
-      <c r="F399" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F399" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="400">
@@ -11437,8 +11438,8 @@
       <c r="E400" t="n">
         <v>0</v>
       </c>
-      <c r="F400" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F400" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="401">
@@ -11463,8 +11464,8 @@
       <c r="E401" t="n">
         <v>0</v>
       </c>
-      <c r="F401" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F401" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="402">
@@ -11489,8 +11490,8 @@
       <c r="E402" t="n">
         <v>0</v>
       </c>
-      <c r="F402" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F402" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="403">
@@ -11515,8 +11516,8 @@
       <c r="E403" t="n">
         <v>0</v>
       </c>
-      <c r="F403" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F403" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="404">
@@ -11541,8 +11542,8 @@
       <c r="E404" t="n">
         <v>0</v>
       </c>
-      <c r="F404" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F404" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="405">
@@ -11567,8 +11568,8 @@
       <c r="E405" t="n">
         <v>0</v>
       </c>
-      <c r="F405" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F405" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="406">
@@ -11593,8 +11594,8 @@
       <c r="E406" t="n">
         <v>0</v>
       </c>
-      <c r="F406" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F406" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="407">
@@ -11619,8 +11620,8 @@
       <c r="E407" t="n">
         <v>0</v>
       </c>
-      <c r="F407" s="23" t="n">
-        <v>45476.56701388889</v>
+      <c r="F407" s="24" t="n">
+        <v>45476.59019675926</v>
       </c>
     </row>
     <row r="408">
@@ -11645,8 +11646,8 @@
       <c r="E408" t="n">
         <v>0</v>
       </c>
-      <c r="F408" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F408" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="409">
@@ -11671,8 +11672,8 @@
       <c r="E409" t="n">
         <v>0</v>
       </c>
-      <c r="F409" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F409" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="410">
@@ -11697,8 +11698,8 @@
       <c r="E410" t="n">
         <v>0</v>
       </c>
-      <c r="F410" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F410" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="411">
@@ -11723,8 +11724,8 @@
       <c r="E411" t="n">
         <v>0</v>
       </c>
-      <c r="F411" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F411" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="412">
@@ -11749,8 +11750,8 @@
       <c r="E412" t="n">
         <v>0</v>
       </c>
-      <c r="F412" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F412" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="413">
@@ -11775,8 +11776,8 @@
       <c r="E413" t="n">
         <v>0</v>
       </c>
-      <c r="F413" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F413" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="414">
@@ -11801,8 +11802,8 @@
       <c r="E414" t="n">
         <v>0</v>
       </c>
-      <c r="F414" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F414" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="415">
@@ -11827,8 +11828,8 @@
       <c r="E415" t="n">
         <v>0</v>
       </c>
-      <c r="F415" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F415" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="416">
@@ -11853,8 +11854,8 @@
       <c r="E416" t="n">
         <v>0</v>
       </c>
-      <c r="F416" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F416" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="417">
@@ -11879,8 +11880,8 @@
       <c r="E417" t="n">
         <v>0</v>
       </c>
-      <c r="F417" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F417" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="418">
@@ -11905,8 +11906,8 @@
       <c r="E418" t="n">
         <v>0</v>
       </c>
-      <c r="F418" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F418" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="419">
@@ -11931,8 +11932,8 @@
       <c r="E419" t="n">
         <v>0</v>
       </c>
-      <c r="F419" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F419" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="420">
@@ -11957,8 +11958,8 @@
       <c r="E420" t="n">
         <v>0</v>
       </c>
-      <c r="F420" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F420" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="421">
@@ -11983,8 +11984,8 @@
       <c r="E421" t="n">
         <v>0</v>
       </c>
-      <c r="F421" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F421" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="422">
@@ -12009,8 +12010,8 @@
       <c r="E422" t="n">
         <v>0</v>
       </c>
-      <c r="F422" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F422" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="423">
@@ -12035,8 +12036,8 @@
       <c r="E423" t="n">
         <v>0</v>
       </c>
-      <c r="F423" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F423" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="424">
@@ -12061,8 +12062,8 @@
       <c r="E424" t="n">
         <v>0</v>
       </c>
-      <c r="F424" s="23" t="n">
-        <v>45476.56702546297</v>
+      <c r="F424" s="24" t="n">
+        <v>45476.59020833333</v>
       </c>
     </row>
     <row r="425">
@@ -12087,8 +12088,8 @@
       <c r="E425" t="n">
         <v>0</v>
       </c>
-      <c r="F425" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F425" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="426">
@@ -12113,8 +12114,8 @@
       <c r="E426" t="n">
         <v>0</v>
       </c>
-      <c r="F426" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F426" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="427">
@@ -12139,8 +12140,8 @@
       <c r="E427" t="n">
         <v>0</v>
       </c>
-      <c r="F427" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F427" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="428">
@@ -12165,8 +12166,8 @@
       <c r="E428" t="n">
         <v>0</v>
       </c>
-      <c r="F428" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F428" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="429">
@@ -12191,8 +12192,8 @@
       <c r="E429" t="n">
         <v>0</v>
       </c>
-      <c r="F429" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F429" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="430">
@@ -12217,8 +12218,8 @@
       <c r="E430" t="n">
         <v>0</v>
       </c>
-      <c r="F430" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F430" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="431">
@@ -12243,8 +12244,8 @@
       <c r="E431" t="n">
         <v>0</v>
       </c>
-      <c r="F431" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F431" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="432">
@@ -12269,8 +12270,8 @@
       <c r="E432" t="n">
         <v>0</v>
       </c>
-      <c r="F432" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F432" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="433">
@@ -12295,8 +12296,8 @@
       <c r="E433" t="n">
         <v>0</v>
       </c>
-      <c r="F433" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F433" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="434">
@@ -12321,8 +12322,8 @@
       <c r="E434" t="n">
         <v>0</v>
       </c>
-      <c r="F434" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F434" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="435">
@@ -12347,8 +12348,8 @@
       <c r="E435" t="n">
         <v>0</v>
       </c>
-      <c r="F435" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F435" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="436">
@@ -12373,8 +12374,8 @@
       <c r="E436" t="n">
         <v>0</v>
       </c>
-      <c r="F436" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F436" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="437">
@@ -12399,8 +12400,8 @@
       <c r="E437" t="n">
         <v>0</v>
       </c>
-      <c r="F437" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F437" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="438">
@@ -12425,8 +12426,8 @@
       <c r="E438" t="n">
         <v>0</v>
       </c>
-      <c r="F438" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F438" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="439">
@@ -12451,8 +12452,8 @@
       <c r="E439" t="n">
         <v>0</v>
       </c>
-      <c r="F439" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F439" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="440">
@@ -12477,8 +12478,8 @@
       <c r="E440" t="n">
         <v>0</v>
       </c>
-      <c r="F440" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F440" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="441">
@@ -12503,8 +12504,8 @@
       <c r="E441" t="n">
         <v>0</v>
       </c>
-      <c r="F441" s="23" t="n">
-        <v>45476.56704861111</v>
+      <c r="F441" s="24" t="n">
+        <v>45476.5902199074</v>
       </c>
     </row>
     <row r="442">
@@ -12529,8 +12530,8 @@
       <c r="E442" t="n">
         <v>0</v>
       </c>
-      <c r="F442" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F442" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="443">
@@ -12555,8 +12556,8 @@
       <c r="E443" t="n">
         <v>0</v>
       </c>
-      <c r="F443" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F443" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="444">
@@ -12581,8 +12582,8 @@
       <c r="E444" t="n">
         <v>0</v>
       </c>
-      <c r="F444" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F444" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="445">
@@ -12607,8 +12608,8 @@
       <c r="E445" t="n">
         <v>0</v>
       </c>
-      <c r="F445" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F445" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="446">
@@ -12633,8 +12634,8 @@
       <c r="E446" t="n">
         <v>0</v>
       </c>
-      <c r="F446" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F446" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="447">
@@ -12659,8 +12660,8 @@
       <c r="E447" t="n">
         <v>0</v>
       </c>
-      <c r="F447" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F447" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="448">
@@ -12685,8 +12686,8 @@
       <c r="E448" t="n">
         <v>0</v>
       </c>
-      <c r="F448" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F448" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="449">
@@ -12711,8 +12712,8 @@
       <c r="E449" t="n">
         <v>0</v>
       </c>
-      <c r="F449" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F449" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="450">
@@ -12737,8 +12738,8 @@
       <c r="E450" t="n">
         <v>0</v>
       </c>
-      <c r="F450" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F450" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="451">
@@ -12763,8 +12764,8 @@
       <c r="E451" t="n">
         <v>0</v>
       </c>
-      <c r="F451" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F451" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="452">
@@ -12789,8 +12790,8 @@
       <c r="E452" t="n">
         <v>0</v>
       </c>
-      <c r="F452" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F452" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="453">
@@ -12815,8 +12816,8 @@
       <c r="E453" t="n">
         <v>0</v>
       </c>
-      <c r="F453" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F453" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="454">
@@ -12841,8 +12842,8 @@
       <c r="E454" t="n">
         <v>0</v>
       </c>
-      <c r="F454" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F454" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="455">
@@ -12867,8 +12868,8 @@
       <c r="E455" t="n">
         <v>0</v>
       </c>
-      <c r="F455" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F455" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="456">
@@ -12893,8 +12894,8 @@
       <c r="E456" t="n">
         <v>0</v>
       </c>
-      <c r="F456" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F456" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="457">
@@ -12919,8 +12920,8 @@
       <c r="E457" t="n">
         <v>0</v>
       </c>
-      <c r="F457" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F457" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="458">
@@ -12945,8 +12946,8 @@
       <c r="E458" t="n">
         <v>0</v>
       </c>
-      <c r="F458" s="23" t="n">
-        <v>45476.56706018518</v>
+      <c r="F458" s="24" t="n">
+        <v>45476.59023148148</v>
       </c>
     </row>
     <row r="459">
@@ -12971,8 +12972,8 @@
       <c r="E459" t="n">
         <v>0</v>
       </c>
-      <c r="F459" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F459" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="460">
@@ -12997,8 +12998,8 @@
       <c r="E460" t="n">
         <v>0</v>
       </c>
-      <c r="F460" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F460" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="461">
@@ -13023,8 +13024,8 @@
       <c r="E461" t="n">
         <v>0</v>
       </c>
-      <c r="F461" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F461" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="462">
@@ -13049,8 +13050,8 @@
       <c r="E462" t="n">
         <v>0</v>
       </c>
-      <c r="F462" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F462" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="463">
@@ -13075,8 +13076,8 @@
       <c r="E463" t="n">
         <v>0</v>
       </c>
-      <c r="F463" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F463" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="464">
@@ -13101,8 +13102,8 @@
       <c r="E464" t="n">
         <v>0</v>
       </c>
-      <c r="F464" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F464" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="465">
@@ -13127,8 +13128,8 @@
       <c r="E465" t="n">
         <v>0</v>
       </c>
-      <c r="F465" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F465" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="466">
@@ -13153,8 +13154,8 @@
       <c r="E466" t="n">
         <v>0</v>
       </c>
-      <c r="F466" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F466" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="467">
@@ -13179,8 +13180,8 @@
       <c r="E467" t="n">
         <v>0</v>
       </c>
-      <c r="F467" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F467" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="468">
@@ -13205,8 +13206,8 @@
       <c r="E468" t="n">
         <v>0</v>
       </c>
-      <c r="F468" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F468" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="469">
@@ -13231,8 +13232,8 @@
       <c r="E469" t="n">
         <v>0</v>
       </c>
-      <c r="F469" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F469" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="470">
@@ -13257,8 +13258,8 @@
       <c r="E470" t="n">
         <v>0</v>
       </c>
-      <c r="F470" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F470" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="471">
@@ -13283,8 +13284,8 @@
       <c r="E471" t="n">
         <v>0</v>
       </c>
-      <c r="F471" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F471" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="472">
@@ -13309,8 +13310,8 @@
       <c r="E472" t="n">
         <v>0</v>
       </c>
-      <c r="F472" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F472" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="473">
@@ -13335,8 +13336,8 @@
       <c r="E473" t="n">
         <v>0</v>
       </c>
-      <c r="F473" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F473" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="474">
@@ -13361,8 +13362,8 @@
       <c r="E474" t="n">
         <v>0</v>
       </c>
-      <c r="F474" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F474" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="475">
@@ -13387,8 +13388,8 @@
       <c r="E475" t="n">
         <v>0</v>
       </c>
-      <c r="F475" s="23" t="n">
-        <v>45476.56707175926</v>
+      <c r="F475" s="24" t="n">
+        <v>45476.59024305556</v>
       </c>
     </row>
     <row r="476">
@@ -13409,8 +13410,8 @@
       <c r="E476" t="n">
         <v>0</v>
       </c>
-      <c r="F476" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F476" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="477">
@@ -13435,8 +13436,8 @@
       <c r="E477" t="n">
         <v>0</v>
       </c>
-      <c r="F477" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F477" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="478">
@@ -13461,8 +13462,8 @@
       <c r="E478" t="n">
         <v>0</v>
       </c>
-      <c r="F478" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F478" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="479">
@@ -13487,8 +13488,8 @@
       <c r="E479" t="n">
         <v>0</v>
       </c>
-      <c r="F479" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F479" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="480">
@@ -13513,8 +13514,8 @@
       <c r="E480" t="n">
         <v>0</v>
       </c>
-      <c r="F480" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F480" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="481">
@@ -13539,8 +13540,8 @@
       <c r="E481" t="n">
         <v>0</v>
       </c>
-      <c r="F481" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F481" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="482">
@@ -13565,8 +13566,8 @@
       <c r="E482" t="n">
         <v>0</v>
       </c>
-      <c r="F482" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F482" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="483">
@@ -13591,8 +13592,8 @@
       <c r="E483" t="n">
         <v>0</v>
       </c>
-      <c r="F483" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F483" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="484">
@@ -13617,8 +13618,8 @@
       <c r="E484" t="n">
         <v>0</v>
       </c>
-      <c r="F484" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F484" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="485">
@@ -13643,8 +13644,8 @@
       <c r="E485" t="n">
         <v>0</v>
       </c>
-      <c r="F485" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F485" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="486">
@@ -13669,8 +13670,8 @@
       <c r="E486" t="n">
         <v>0</v>
       </c>
-      <c r="F486" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F486" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="487">
@@ -13695,8 +13696,8 @@
       <c r="E487" t="n">
         <v>0</v>
       </c>
-      <c r="F487" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F487" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="488">
@@ -13721,8 +13722,8 @@
       <c r="E488" t="n">
         <v>0</v>
       </c>
-      <c r="F488" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F488" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="489">
@@ -13747,8 +13748,8 @@
       <c r="E489" t="n">
         <v>0</v>
       </c>
-      <c r="F489" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F489" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="490">
@@ -13773,8 +13774,8 @@
       <c r="E490" t="n">
         <v>0</v>
       </c>
-      <c r="F490" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F490" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="491">
@@ -13799,8 +13800,8 @@
       <c r="E491" t="n">
         <v>0</v>
       </c>
-      <c r="F491" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F491" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="492">
@@ -13825,8 +13826,8 @@
       <c r="E492" t="n">
         <v>0</v>
       </c>
-      <c r="F492" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F492" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="493">
@@ -13851,8 +13852,8 @@
       <c r="E493" t="n">
         <v>0</v>
       </c>
-      <c r="F493" s="23" t="n">
-        <v>45476.56708333334</v>
+      <c r="F493" s="24" t="n">
+        <v>45476.59025462963</v>
       </c>
     </row>
     <row r="494">
@@ -13873,8 +13874,8 @@
       <c r="E494" t="n">
         <v>0</v>
       </c>
-      <c r="F494" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F494" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="495">
@@ -13899,8 +13900,8 @@
       <c r="E495" t="n">
         <v>0</v>
       </c>
-      <c r="F495" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F495" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="496">
@@ -13925,8 +13926,8 @@
       <c r="E496" t="n">
         <v>0</v>
       </c>
-      <c r="F496" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F496" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="497">
@@ -13951,8 +13952,8 @@
       <c r="E497" t="n">
         <v>0</v>
       </c>
-      <c r="F497" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F497" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="498">
@@ -13977,8 +13978,8 @@
       <c r="E498" t="n">
         <v>0</v>
       </c>
-      <c r="F498" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F498" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="499">
@@ -14003,8 +14004,8 @@
       <c r="E499" t="n">
         <v>0</v>
       </c>
-      <c r="F499" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F499" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="500">
@@ -14029,8 +14030,8 @@
       <c r="E500" t="n">
         <v>0</v>
       </c>
-      <c r="F500" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F500" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="501">
@@ -14055,8 +14056,8 @@
       <c r="E501" t="n">
         <v>0</v>
       </c>
-      <c r="F501" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F501" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="502">
@@ -14081,8 +14082,8 @@
       <c r="E502" t="n">
         <v>0</v>
       </c>
-      <c r="F502" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F502" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="503">
@@ -14107,8 +14108,8 @@
       <c r="E503" t="n">
         <v>0</v>
       </c>
-      <c r="F503" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F503" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="504">
@@ -14133,8 +14134,8 @@
       <c r="E504" t="n">
         <v>0</v>
       </c>
-      <c r="F504" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F504" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="505">
@@ -14159,8 +14160,8 @@
       <c r="E505" t="n">
         <v>0</v>
       </c>
-      <c r="F505" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F505" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="506">
@@ -14185,8 +14186,8 @@
       <c r="E506" t="n">
         <v>0</v>
       </c>
-      <c r="F506" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F506" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="507">
@@ -14211,8 +14212,8 @@
       <c r="E507" t="n">
         <v>0</v>
       </c>
-      <c r="F507" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F507" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="508">
@@ -14237,8 +14238,8 @@
       <c r="E508" t="n">
         <v>0</v>
       </c>
-      <c r="F508" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F508" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="509">
@@ -14263,8 +14264,8 @@
       <c r="E509" t="n">
         <v>0</v>
       </c>
-      <c r="F509" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F509" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="510">
@@ -14289,8 +14290,8 @@
       <c r="E510" t="n">
         <v>0</v>
       </c>
-      <c r="F510" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F510" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="511">
@@ -14315,8 +14316,8 @@
       <c r="E511" t="n">
         <v>0</v>
       </c>
-      <c r="F511" s="23" t="n">
-        <v>45476.5670949074</v>
+      <c r="F511" s="24" t="n">
+        <v>45476.5902662037</v>
       </c>
     </row>
     <row r="512">
@@ -14341,8 +14342,8 @@
       <c r="E512" t="n">
         <v>0</v>
       </c>
-      <c r="F512" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F512" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="513">
@@ -14367,8 +14368,8 @@
       <c r="E513" t="n">
         <v>0</v>
       </c>
-      <c r="F513" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F513" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="514">
@@ -14393,8 +14394,8 @@
       <c r="E514" t="n">
         <v>0</v>
       </c>
-      <c r="F514" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F514" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="515">
@@ -14419,8 +14420,8 @@
       <c r="E515" t="n">
         <v>0</v>
       </c>
-      <c r="F515" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F515" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="516">
@@ -14445,8 +14446,8 @@
       <c r="E516" t="n">
         <v>0</v>
       </c>
-      <c r="F516" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F516" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="517">
@@ -14471,8 +14472,8 @@
       <c r="E517" t="n">
         <v>0</v>
       </c>
-      <c r="F517" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F517" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="518">
@@ -14497,8 +14498,8 @@
       <c r="E518" t="n">
         <v>0</v>
       </c>
-      <c r="F518" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F518" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="519">
@@ -14523,8 +14524,8 @@
       <c r="E519" t="n">
         <v>0</v>
       </c>
-      <c r="F519" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F519" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="520">
@@ -14549,8 +14550,8 @@
       <c r="E520" t="n">
         <v>0</v>
       </c>
-      <c r="F520" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F520" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="521">
@@ -14575,8 +14576,8 @@
       <c r="E521" t="n">
         <v>0</v>
       </c>
-      <c r="F521" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F521" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="522">
@@ -14601,8 +14602,8 @@
       <c r="E522" t="n">
         <v>0</v>
       </c>
-      <c r="F522" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F522" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="523">
@@ -14627,8 +14628,8 @@
       <c r="E523" t="n">
         <v>0</v>
       </c>
-      <c r="F523" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F523" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="524">
@@ -14653,8 +14654,8 @@
       <c r="E524" t="n">
         <v>0</v>
       </c>
-      <c r="F524" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F524" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="525">
@@ -14679,8 +14680,8 @@
       <c r="E525" t="n">
         <v>0</v>
       </c>
-      <c r="F525" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F525" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="526">
@@ -14705,8 +14706,8 @@
       <c r="E526" t="n">
         <v>0</v>
       </c>
-      <c r="F526" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F526" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="527">
@@ -14731,8 +14732,8 @@
       <c r="E527" t="n">
         <v>0</v>
       </c>
-      <c r="F527" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F527" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
     <row r="528">
@@ -14757,8 +14758,8 @@
       <c r="E528" t="n">
         <v>0</v>
       </c>
-      <c r="F528" s="23" t="n">
-        <v>45476.56710648148</v>
+      <c r="F528" s="24" t="n">
+        <v>45476.59028935185</v>
       </c>
     </row>
   </sheetData>

--- a/kream_test_data.xlsx
+++ b/kream_test_data.xlsx
@@ -1099,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="3">
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="4">
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="5">
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="6">
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="7">
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="8">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="9">
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="10">
@@ -1307,7 +1307,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="11">
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="12">
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="13">
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="14">
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="15">
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="16">
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="17">
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="18">
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>45476.58987268519</v>
+        <v>45476.75450231481</v>
       </c>
     </row>
     <row r="19">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="20">
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="21">
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="22">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="23">
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="24">
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="25">
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="26">
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="27">
@@ -1749,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="28">
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="29">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="30">
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="31">
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="32">
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="33">
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="34">
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="35">
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="24" t="n">
-        <v>45476.58989583333</v>
+        <v>45476.75451388889</v>
       </c>
     </row>
     <row r="36">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="37">
@@ -2009,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="38">
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="39">
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="40">
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="41">
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="42">
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="43">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="44">
@@ -2191,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="45">
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="46">
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="47">
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="48">
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="49">
@@ -2321,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="50">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="51">
@@ -2373,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="52">
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="24" t="n">
-        <v>45476.5899074074</v>
+        <v>45476.75452546297</v>
       </c>
     </row>
     <row r="53">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="54">
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="55">
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="56">
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="57">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="58">
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="59">
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="60">
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="61">
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="62">
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="63">
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="64">
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="65">
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="66">
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="67">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="68">
@@ -2815,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="F68" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="69">
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="24" t="n">
-        <v>45476.58991898148</v>
+        <v>45476.75453703704</v>
       </c>
     </row>
     <row r="70">
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="24" t="n">
-        <v>45476.58993055556</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="71">
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="24" t="n">
-        <v>45476.58993055556</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="72">
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="24" t="n">
-        <v>45476.58993055556</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="73">
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="24" t="n">
-        <v>45476.58993055556</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="74">
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="24" t="n">
-        <v>45476.58993055556</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="75">
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="24" t="n">
-        <v>45476.58993055556</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="76">
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="24" t="n">
-        <v>45476.58993055556</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="77">
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="24" t="n">
-        <v>45476.58993055556</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="78">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="24" t="n">
-        <v>45476.58993055556</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="79">
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="24" t="n">
-        <v>45476.58993055556</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="80">
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="24" t="n">
-        <v>45476.5899537037</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="81">
@@ -3153,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="24" t="n">
-        <v>45476.5899537037</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="82">
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="24" t="n">
-        <v>45476.5899537037</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="83">
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="24" t="n">
-        <v>45476.5899537037</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="84">
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="24" t="n">
-        <v>45476.5899537037</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="85">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="24" t="n">
-        <v>45476.5899537037</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="86">
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="24" t="n">
-        <v>45476.5899537037</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="87">
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="24" t="n">
-        <v>45476.5899537037</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="88">
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="F88" s="24" t="n">
-        <v>45476.5899537037</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="89">
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="24" t="n">
-        <v>45476.5899537037</v>
+        <v>45476.75454861111</v>
       </c>
     </row>
     <row r="90">
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="F90" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="91">
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="92">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="F92" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="93">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="94">
@@ -3491,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="95">
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="F95" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="96">
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="F96" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="97">
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="98">
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="99">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="100">
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="F100" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="101">
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="102">
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="F102" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="103">
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="104">
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="105">
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="106">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="24" t="n">
-        <v>45476.58996527778</v>
+        <v>45476.75456018518</v>
       </c>
     </row>
     <row r="107">
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="24" t="n">
-        <v>45476.58997685185</v>
+        <v>45476.75457175926</v>
       </c>
     </row>
     <row r="108">
@@ -3855,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="F108" s="24" t="n">
-        <v>45476.58997685185</v>
+        <v>45476.75457175926</v>
       </c>
     </row>
     <row r="109">
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="24" t="n">
-        <v>45476.58997685185</v>
+        <v>45476.75457175926</v>
       </c>
     </row>
     <row r="110">
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="24" t="n">
-        <v>45476.58997685185</v>
+        <v>45476.75457175926</v>
       </c>
     </row>
     <row r="111">
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="24" t="n">
-        <v>45476.58997685185</v>
+        <v>45476.75457175926</v>
       </c>
     </row>
     <row r="112">
@@ -3959,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="24" t="n">
-        <v>45476.58997685185</v>
+        <v>45476.75457175926</v>
       </c>
     </row>
     <row r="113">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="F113" s="24" t="n">
-        <v>45476.58997685185</v>
+        <v>45476.75457175926</v>
       </c>
     </row>
     <row r="114">
@@ -4011,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="24" t="n">
-        <v>45476.58997685185</v>
+        <v>45476.75457175926</v>
       </c>
     </row>
     <row r="115">
@@ -4037,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="24" t="n">
-        <v>45476.58997685185</v>
+        <v>45476.75457175926</v>
       </c>
     </row>
     <row r="116">
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="F116" s="24" t="n">
-        <v>45476.58997685185</v>
+        <v>45476.75457175926</v>
       </c>
     </row>
     <row r="117">
@@ -4089,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="F117" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="118">
@@ -4115,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="119">
@@ -4141,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="120">
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="121">
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="F121" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="122">
@@ -4219,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="F122" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="123">
@@ -4245,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="124">
@@ -4271,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="F124" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="125">
@@ -4297,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="126">
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="127">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="128">
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="F128" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="129">
@@ -4401,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="F129" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="130">
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="F130" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="131">
@@ -4453,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="132">
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="F132" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="133">
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="F133" s="24" t="n">
-        <v>45476.58998842593</v>
+        <v>45476.75458333334</v>
       </c>
     </row>
     <row r="134">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="135">
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="F135" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="136">
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="F136" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="137">
@@ -4609,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="F137" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="138">
@@ -4635,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="F138" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="139">
@@ -4661,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="F139" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="140">
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="F140" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="141">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="F141" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="142">
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="F142" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="143">
@@ -4765,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="F143" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="144">
@@ -4791,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="F144" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="145">
@@ -4817,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="F145" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="146">
@@ -4843,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="F146" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="147">
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="F147" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="148">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="F148" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="149">
@@ -4921,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="F149" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="150">
@@ -4947,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="F150" s="24" t="n">
-        <v>45476.59</v>
+        <v>45476.75460648148</v>
       </c>
     </row>
     <row r="151">
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="F151" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="152">
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="F152" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="153">
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="F153" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="154">
@@ -5051,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="F154" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="155">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="F155" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="156">
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="F156" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="157">
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="F157" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="158">
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="F158" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="159">
@@ -5181,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="F159" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="160">
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="F160" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="161">
@@ -5233,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="F161" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="162">
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="F162" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="163">
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="F163" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="164">
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="F164" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="165">
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="F165" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="166">
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="F166" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="167">
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="F167" s="24" t="n">
-        <v>45476.59001157407</v>
+        <v>45476.75461805556</v>
       </c>
     </row>
     <row r="168">
@@ -5411,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="F168" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="169">
@@ -5437,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="F169" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="170">
@@ -5463,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="F170" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="171">
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="F171" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="172">
@@ -5515,7 +5515,7 @@
         <v>0</v>
       </c>
       <c r="F172" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="173">
@@ -5541,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="F173" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="174">
@@ -5567,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="F174" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="175">
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="F175" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="176">
@@ -5619,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="F176" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="177">
@@ -5645,7 +5645,7 @@
         <v>0</v>
       </c>
       <c r="F177" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="178">
@@ -5671,7 +5671,7 @@
         <v>0</v>
       </c>
       <c r="F178" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="179">
@@ -5697,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="F179" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="180">
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="F180" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="181">
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="F181" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="182">
@@ -5775,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="F182" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="183">
@@ -5801,7 +5801,7 @@
         <v>0</v>
       </c>
       <c r="F183" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="184">
@@ -5827,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="F184" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="185">
@@ -5853,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="F185" s="24" t="n">
-        <v>45476.59002314815</v>
+        <v>45476.75462962963</v>
       </c>
     </row>
     <row r="186">
@@ -5879,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="F186" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="187">
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="F187" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="188">
@@ -5931,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="F188" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="189">
@@ -5957,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="F189" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="190">
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="F190" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="191">
@@ -6009,7 +6009,7 @@
         <v>0</v>
       </c>
       <c r="F191" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="192">
@@ -6035,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="F192" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="193">
@@ -6061,7 +6061,7 @@
         <v>0</v>
       </c>
       <c r="F193" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="194">
@@ -6087,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="F194" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="195">
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="F195" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="196">
@@ -6139,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="F196" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="197">
@@ -6165,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="F197" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="198">
@@ -6191,7 +6191,7 @@
         <v>0</v>
       </c>
       <c r="F198" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="199">
@@ -6217,7 +6217,7 @@
         <v>0</v>
       </c>
       <c r="F199" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="200">
@@ -6243,7 +6243,7 @@
         <v>0</v>
       </c>
       <c r="F200" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="201">
@@ -6269,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="F201" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="202">
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="F202" s="24" t="n">
-        <v>45476.5900462963</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="203">
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="F203" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="204">
@@ -6347,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="F204" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="205">
@@ -6373,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="F205" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="206">
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="F206" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="207">
@@ -6425,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="F207" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="208">
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="F208" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="209">
@@ -6477,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="F209" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="210">
@@ -6503,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="F210" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="211">
@@ -6529,7 +6529,7 @@
         <v>0</v>
       </c>
       <c r="F211" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="212">
@@ -6555,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="F212" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="213">
@@ -6581,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="F213" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="214">
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="F214" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="215">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="F215" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="216">
@@ -6659,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="F216" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="217">
@@ -6685,7 +6685,7 @@
         <v>0</v>
       </c>
       <c r="F217" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="218">
@@ -6711,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="F218" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="219">
@@ -6737,7 +6737,7 @@
         <v>0</v>
       </c>
       <c r="F219" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.7546412037</v>
       </c>
     </row>
     <row r="220">
@@ -6763,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="F220" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="221">
@@ -6789,7 +6789,7 @@
         <v>0</v>
       </c>
       <c r="F221" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="222">
@@ -6815,7 +6815,7 @@
         <v>0</v>
       </c>
       <c r="F222" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="223">
@@ -6841,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="F223" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="224">
@@ -6867,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="F224" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="225">
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="F225" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="226">
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="F226" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="227">
@@ -6945,7 +6945,7 @@
         <v>0</v>
       </c>
       <c r="F227" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="228">
@@ -6971,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="F228" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="229">
@@ -6997,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="F229" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="230">
@@ -7023,7 +7023,7 @@
         <v>0</v>
       </c>
       <c r="F230" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="231">
@@ -7049,7 +7049,7 @@
         <v>0</v>
       </c>
       <c r="F231" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="232">
@@ -7075,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="F232" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="233">
@@ -7101,7 +7101,7 @@
         <v>0</v>
       </c>
       <c r="F233" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="234">
@@ -7127,7 +7127,7 @@
         <v>0</v>
       </c>
       <c r="F234" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="235">
@@ -7153,7 +7153,7 @@
         <v>0</v>
       </c>
       <c r="F235" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="236">
@@ -7179,7 +7179,7 @@
         <v>0</v>
       </c>
       <c r="F236" s="24" t="n">
-        <v>45476.59005787037</v>
+        <v>45476.75465277778</v>
       </c>
     </row>
     <row r="237">
@@ -7205,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="F237" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="238">
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="F238" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="239">
@@ -7257,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="F239" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="240">
@@ -7283,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="F240" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="241">
@@ -7309,7 +7309,7 @@
         <v>0</v>
       </c>
       <c r="F241" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="242">
@@ -7335,7 +7335,7 @@
         <v>0</v>
       </c>
       <c r="F242" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="243">
@@ -7361,7 +7361,7 @@
         <v>0</v>
       </c>
       <c r="F243" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="244">
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="F244" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="245">
@@ -7413,7 +7413,7 @@
         <v>0</v>
       </c>
       <c r="F245" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="246">
@@ -7439,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="F246" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="247">
@@ -7465,7 +7465,7 @@
         <v>0</v>
       </c>
       <c r="F247" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="248">
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="F248" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="249">
@@ -7517,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="F249" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="250">
@@ -7543,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="F250" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="251">
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="F251" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="252">
@@ -7595,7 +7595,7 @@
         <v>0</v>
       </c>
       <c r="F252" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="253">
@@ -7621,7 +7621,7 @@
         <v>0</v>
       </c>
       <c r="F253" s="24" t="n">
-        <v>45476.59008101852</v>
+        <v>45476.75466435185</v>
       </c>
     </row>
     <row r="254">
@@ -7647,7 +7647,7 @@
         <v>0</v>
       </c>
       <c r="F254" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="255">
@@ -7673,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="F255" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="256">
@@ -7699,7 +7699,7 @@
         <v>0</v>
       </c>
       <c r="F256" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="257">
@@ -7725,7 +7725,7 @@
         <v>0</v>
       </c>
       <c r="F257" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="258">
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="F258" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="259">
@@ -7777,7 +7777,7 @@
         <v>0</v>
       </c>
       <c r="F259" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="260">
@@ -7803,7 +7803,7 @@
         <v>0</v>
       </c>
       <c r="F260" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="261">
@@ -7829,7 +7829,7 @@
         <v>0</v>
       </c>
       <c r="F261" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="262">
@@ -7855,7 +7855,7 @@
         <v>0</v>
       </c>
       <c r="F262" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="263">
@@ -7881,7 +7881,7 @@
         <v>0</v>
       </c>
       <c r="F263" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="264">
@@ -7907,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="F264" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="265">
@@ -7933,7 +7933,7 @@
         <v>0</v>
       </c>
       <c r="F265" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="266">
@@ -7959,7 +7959,7 @@
         <v>0</v>
       </c>
       <c r="F266" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="267">
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="F267" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="268">
@@ -8011,7 +8011,7 @@
         <v>0</v>
       </c>
       <c r="F268" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="269">
@@ -8037,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="F269" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="270">
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="F270" s="24" t="n">
-        <v>45476.5900925926</v>
+        <v>45476.75467592593</v>
       </c>
     </row>
     <row r="271">
@@ -8089,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="F271" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="272">
@@ -8115,7 +8115,7 @@
         <v>0</v>
       </c>
       <c r="F272" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="273">
@@ -8141,7 +8141,7 @@
         <v>0</v>
       </c>
       <c r="F273" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="274">
@@ -8167,7 +8167,7 @@
         <v>0</v>
       </c>
       <c r="F274" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="275">
@@ -8193,7 +8193,7 @@
         <v>0</v>
       </c>
       <c r="F275" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="276">
@@ -8219,7 +8219,7 @@
         <v>0</v>
       </c>
       <c r="F276" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="277">
@@ -8245,7 +8245,7 @@
         <v>0</v>
       </c>
       <c r="F277" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="278">
@@ -8271,7 +8271,7 @@
         <v>0</v>
       </c>
       <c r="F278" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="279">
@@ -8297,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="F279" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="280">
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="F280" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="281">
@@ -8349,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="F281" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="282">
@@ -8375,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="F282" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="283">
@@ -8401,7 +8401,7 @@
         <v>0</v>
       </c>
       <c r="F283" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="284">
@@ -8427,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="F284" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="285">
@@ -8453,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="F285" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="286">
@@ -8479,7 +8479,7 @@
         <v>0</v>
       </c>
       <c r="F286" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="287">
@@ -8505,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="F287" s="24" t="n">
-        <v>45476.59010416667</v>
+        <v>45476.7546875</v>
       </c>
     </row>
     <row r="288">
@@ -8531,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="F288" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="289">
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="F289" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="290">
@@ -8583,7 +8583,7 @@
         <v>0</v>
       </c>
       <c r="F290" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="291">
@@ -8609,7 +8609,7 @@
         <v>0</v>
       </c>
       <c r="F291" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="292">
@@ -8635,7 +8635,7 @@
         <v>0</v>
       </c>
       <c r="F292" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="293">
@@ -8661,7 +8661,7 @@
         <v>0</v>
       </c>
       <c r="F293" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="294">
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="F294" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="295">
@@ -8713,7 +8713,7 @@
         <v>0</v>
       </c>
       <c r="F295" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="296">
@@ -8739,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="F296" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="297">
@@ -8765,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="F297" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="298">
@@ -8791,7 +8791,7 @@
         <v>0</v>
       </c>
       <c r="F298" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="299">
@@ -8817,7 +8817,7 @@
         <v>0</v>
       </c>
       <c r="F299" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="300">
@@ -8843,7 +8843,7 @@
         <v>0</v>
       </c>
       <c r="F300" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="301">
@@ -8869,7 +8869,7 @@
         <v>0</v>
       </c>
       <c r="F301" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="302">
@@ -8895,7 +8895,7 @@
         <v>0</v>
       </c>
       <c r="F302" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="303">
@@ -8921,7 +8921,7 @@
         <v>0</v>
       </c>
       <c r="F303" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="304">
@@ -8947,7 +8947,7 @@
         <v>0</v>
       </c>
       <c r="F304" s="24" t="n">
-        <v>45476.59012731481</v>
+        <v>45476.75469907407</v>
       </c>
     </row>
     <row r="305">
@@ -8973,7 +8973,7 @@
         <v>0</v>
       </c>
       <c r="F305" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="306">
@@ -8999,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="F306" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="307">
@@ -9025,7 +9025,7 @@
         <v>0</v>
       </c>
       <c r="F307" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="308">
@@ -9051,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="F308" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="309">
@@ -9077,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="F309" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="310">
@@ -9103,7 +9103,7 @@
         <v>0</v>
       </c>
       <c r="F310" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="311">
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="F311" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="312">
@@ -9155,7 +9155,7 @@
         <v>0</v>
       </c>
       <c r="F312" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="313">
@@ -9181,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="F313" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="314">
@@ -9207,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="F314" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="315">
@@ -9233,7 +9233,7 @@
         <v>0</v>
       </c>
       <c r="F315" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="316">
@@ -9259,7 +9259,7 @@
         <v>0</v>
       </c>
       <c r="F316" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="317">
@@ -9285,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="F317" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="318">
@@ -9311,7 +9311,7 @@
         <v>0</v>
       </c>
       <c r="F318" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="319">
@@ -9337,7 +9337,7 @@
         <v>0</v>
       </c>
       <c r="F319" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="320">
@@ -9363,7 +9363,7 @@
         <v>0</v>
       </c>
       <c r="F320" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="321">
@@ -9389,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="F321" s="24" t="n">
-        <v>45476.59013888889</v>
+        <v>45476.75471064815</v>
       </c>
     </row>
     <row r="322">
@@ -9411,7 +9411,7 @@
         <v>0</v>
       </c>
       <c r="F322" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="323">
@@ -9437,7 +9437,7 @@
         <v>0</v>
       </c>
       <c r="F323" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="324">
@@ -9463,7 +9463,7 @@
         <v>0</v>
       </c>
       <c r="F324" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="325">
@@ -9489,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="F325" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="326">
@@ -9515,7 +9515,7 @@
         <v>0</v>
       </c>
       <c r="F326" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="327">
@@ -9541,7 +9541,7 @@
         <v>0</v>
       </c>
       <c r="F327" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="328">
@@ -9567,7 +9567,7 @@
         <v>0</v>
       </c>
       <c r="F328" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="329">
@@ -9593,7 +9593,7 @@
         <v>0</v>
       </c>
       <c r="F329" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="330">
@@ -9619,7 +9619,7 @@
         <v>0</v>
       </c>
       <c r="F330" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="331">
@@ -9645,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="F331" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="332">
@@ -9671,7 +9671,7 @@
         <v>0</v>
       </c>
       <c r="F332" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="333">
@@ -9697,7 +9697,7 @@
         <v>0</v>
       </c>
       <c r="F333" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="334">
@@ -9723,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="F334" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="335">
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="F335" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="336">
@@ -9775,7 +9775,7 @@
         <v>0</v>
       </c>
       <c r="F336" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="337">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="F337" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="338">
@@ -9827,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="F338" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="339">
@@ -9853,7 +9853,7 @@
         <v>0</v>
       </c>
       <c r="F339" s="24" t="n">
-        <v>45476.59015046297</v>
+        <v>45476.75472222222</v>
       </c>
     </row>
     <row r="340">
@@ -9879,7 +9879,7 @@
         <v>0</v>
       </c>
       <c r="F340" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="341">
@@ -9905,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="F341" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="342">
@@ -9931,7 +9931,7 @@
         <v>0</v>
       </c>
       <c r="F342" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="343">
@@ -9957,7 +9957,7 @@
         <v>0</v>
       </c>
       <c r="F343" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="344">
@@ -9983,7 +9983,7 @@
         <v>0</v>
       </c>
       <c r="F344" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="345">
@@ -10009,7 +10009,7 @@
         <v>0</v>
       </c>
       <c r="F345" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="346">
@@ -10035,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="F346" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="347">
@@ -10061,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="F347" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="348">
@@ -10087,7 +10087,7 @@
         <v>0</v>
       </c>
       <c r="F348" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="349">
@@ -10113,7 +10113,7 @@
         <v>0</v>
       </c>
       <c r="F349" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="350">
@@ -10139,7 +10139,7 @@
         <v>0</v>
       </c>
       <c r="F350" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="351">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="F351" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="352">
@@ -10191,7 +10191,7 @@
         <v>0</v>
       </c>
       <c r="F352" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="353">
@@ -10217,7 +10217,7 @@
         <v>0</v>
       </c>
       <c r="F353" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="354">
@@ -10243,7 +10243,7 @@
         <v>0</v>
       </c>
       <c r="F354" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="355">
@@ -10269,7 +10269,7 @@
         <v>0</v>
       </c>
       <c r="F355" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="356">
@@ -10295,7 +10295,7 @@
         <v>0</v>
       </c>
       <c r="F356" s="24" t="n">
-        <v>45476.59016203704</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="357">
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="F357" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="358">
@@ -10347,7 +10347,7 @@
         <v>0</v>
       </c>
       <c r="F358" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="359">
@@ -10373,7 +10373,7 @@
         <v>0</v>
       </c>
       <c r="F359" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="360">
@@ -10399,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="F360" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="361">
@@ -10425,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="F361" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="362">
@@ -10451,7 +10451,7 @@
         <v>0</v>
       </c>
       <c r="F362" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="363">
@@ -10477,7 +10477,7 @@
         <v>0</v>
       </c>
       <c r="F363" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="364">
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="F364" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="365">
@@ -10529,7 +10529,7 @@
         <v>0</v>
       </c>
       <c r="F365" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="366">
@@ -10555,7 +10555,7 @@
         <v>0</v>
       </c>
       <c r="F366" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="367">
@@ -10581,7 +10581,7 @@
         <v>0</v>
       </c>
       <c r="F367" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="368">
@@ -10607,7 +10607,7 @@
         <v>0</v>
       </c>
       <c r="F368" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="369">
@@ -10633,7 +10633,7 @@
         <v>0</v>
       </c>
       <c r="F369" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="370">
@@ -10659,7 +10659,7 @@
         <v>0</v>
       </c>
       <c r="F370" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="371">
@@ -10685,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="F371" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="372">
@@ -10711,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="F372" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="373">
@@ -10737,7 +10737,7 @@
         <v>0</v>
       </c>
       <c r="F373" s="24" t="n">
-        <v>45476.59017361111</v>
+        <v>45476.7547337963</v>
       </c>
     </row>
     <row r="374">
@@ -10763,7 +10763,7 @@
         <v>0</v>
       </c>
       <c r="F374" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="375">
@@ -10789,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="F375" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="376">
@@ -10815,7 +10815,7 @@
         <v>0</v>
       </c>
       <c r="F376" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="377">
@@ -10841,7 +10841,7 @@
         <v>0</v>
       </c>
       <c r="F377" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="378">
@@ -10867,7 +10867,7 @@
         <v>0</v>
       </c>
       <c r="F378" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="379">
@@ -10893,7 +10893,7 @@
         <v>0</v>
       </c>
       <c r="F379" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="380">
@@ -10919,7 +10919,7 @@
         <v>0</v>
       </c>
       <c r="F380" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="381">
@@ -10945,7 +10945,7 @@
         <v>0</v>
       </c>
       <c r="F381" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="382">
@@ -10971,7 +10971,7 @@
         <v>0</v>
       </c>
       <c r="F382" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="383">
@@ -10997,7 +10997,7 @@
         <v>0</v>
       </c>
       <c r="F383" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="384">
@@ -11023,7 +11023,7 @@
         <v>0</v>
       </c>
       <c r="F384" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="385">
@@ -11049,7 +11049,7 @@
         <v>0</v>
       </c>
       <c r="F385" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="386">
@@ -11075,7 +11075,7 @@
         <v>0</v>
       </c>
       <c r="F386" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="387">
@@ -11101,7 +11101,7 @@
         <v>0</v>
       </c>
       <c r="F387" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="388">
@@ -11127,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="F388" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="389">
@@ -11153,7 +11153,7 @@
         <v>0</v>
       </c>
       <c r="F389" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="390">
@@ -11179,7 +11179,7 @@
         <v>0</v>
       </c>
       <c r="F390" s="24" t="n">
-        <v>45476.59018518519</v>
+        <v>45476.75474537037</v>
       </c>
     </row>
     <row r="391">
@@ -11205,7 +11205,7 @@
         <v>0</v>
       </c>
       <c r="F391" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="392">
@@ -11231,7 +11231,7 @@
         <v>0</v>
       </c>
       <c r="F392" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="393">
@@ -11257,7 +11257,7 @@
         <v>0</v>
       </c>
       <c r="F393" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="394">
@@ -11283,7 +11283,7 @@
         <v>0</v>
       </c>
       <c r="F394" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="395">
@@ -11309,7 +11309,7 @@
         <v>0</v>
       </c>
       <c r="F395" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="396">
@@ -11335,7 +11335,7 @@
         <v>0</v>
       </c>
       <c r="F396" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="397">
@@ -11361,7 +11361,7 @@
         <v>0</v>
       </c>
       <c r="F397" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="398">
@@ -11387,7 +11387,7 @@
         <v>0</v>
       </c>
       <c r="F398" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="399">
@@ -11413,7 +11413,7 @@
         <v>0</v>
       </c>
       <c r="F399" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="400">
@@ -11439,7 +11439,7 @@
         <v>0</v>
       </c>
       <c r="F400" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="401">
@@ -11465,7 +11465,7 @@
         <v>0</v>
       </c>
       <c r="F401" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="402">
@@ -11491,7 +11491,7 @@
         <v>0</v>
       </c>
       <c r="F402" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="403">
@@ -11517,7 +11517,7 @@
         <v>0</v>
       </c>
       <c r="F403" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="404">
@@ -11543,7 +11543,7 @@
         <v>0</v>
       </c>
       <c r="F404" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="405">
@@ -11569,7 +11569,7 @@
         <v>0</v>
       </c>
       <c r="F405" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="406">
@@ -11595,7 +11595,7 @@
         <v>0</v>
       </c>
       <c r="F406" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="407">
@@ -11621,7 +11621,7 @@
         <v>0</v>
       </c>
       <c r="F407" s="24" t="n">
-        <v>45476.59019675926</v>
+        <v>45476.75475694444</v>
       </c>
     </row>
     <row r="408">
@@ -11647,7 +11647,7 @@
         <v>0</v>
       </c>
       <c r="F408" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="409">
@@ -11673,7 +11673,7 @@
         <v>0</v>
       </c>
       <c r="F409" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="410">
@@ -11699,7 +11699,7 @@
         <v>0</v>
       </c>
       <c r="F410" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="411">
@@ -11725,7 +11725,7 @@
         <v>0</v>
       </c>
       <c r="F411" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="412">
@@ -11751,7 +11751,7 @@
         <v>0</v>
       </c>
       <c r="F412" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="413">
@@ -11777,7 +11777,7 @@
         <v>0</v>
       </c>
       <c r="F413" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="414">
@@ -11803,7 +11803,7 @@
         <v>0</v>
       </c>
       <c r="F414" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="415">
@@ -11829,7 +11829,7 @@
         <v>0</v>
       </c>
       <c r="F415" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="416">
@@ -11855,7 +11855,7 @@
         <v>0</v>
       </c>
       <c r="F416" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="417">
@@ -11881,7 +11881,7 @@
         <v>0</v>
       </c>
       <c r="F417" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="418">
@@ -11907,7 +11907,7 @@
         <v>0</v>
       </c>
       <c r="F418" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="419">
@@ -11933,7 +11933,7 @@
         <v>0</v>
       </c>
       <c r="F419" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="420">
@@ -11959,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="F420" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="421">
@@ -11985,7 +11985,7 @@
         <v>0</v>
       </c>
       <c r="F421" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="422">
@@ -12011,7 +12011,7 @@
         <v>0</v>
       </c>
       <c r="F422" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="423">
@@ -12037,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="F423" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="424">
@@ -12063,7 +12063,7 @@
         <v>0</v>
       </c>
       <c r="F424" s="24" t="n">
-        <v>45476.59020833333</v>
+        <v>45476.75476851852</v>
       </c>
     </row>
     <row r="425">
@@ -12089,7 +12089,7 @@
         <v>0</v>
       </c>
       <c r="F425" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="426">
@@ -12115,7 +12115,7 @@
         <v>0</v>
       </c>
       <c r="F426" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="427">
@@ -12141,7 +12141,7 @@
         <v>0</v>
       </c>
       <c r="F427" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="428">
@@ -12167,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="F428" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="429">
@@ -12193,7 +12193,7 @@
         <v>0</v>
       </c>
       <c r="F429" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="430">
@@ -12219,7 +12219,7 @@
         <v>0</v>
       </c>
       <c r="F430" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="431">
@@ -12245,7 +12245,7 @@
         <v>0</v>
       </c>
       <c r="F431" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="432">
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="F432" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="433">
@@ -12297,7 +12297,7 @@
         <v>0</v>
       </c>
       <c r="F433" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="434">
@@ -12323,7 +12323,7 @@
         <v>0</v>
       </c>
       <c r="F434" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="435">
@@ -12349,7 +12349,7 @@
         <v>0</v>
       </c>
       <c r="F435" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="436">
@@ -12375,7 +12375,7 @@
         <v>0</v>
       </c>
       <c r="F436" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="437">
@@ -12401,7 +12401,7 @@
         <v>0</v>
       </c>
       <c r="F437" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="438">
@@ -12427,7 +12427,7 @@
         <v>0</v>
       </c>
       <c r="F438" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="439">
@@ -12453,7 +12453,7 @@
         <v>0</v>
       </c>
       <c r="F439" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="440">
@@ -12479,7 +12479,7 @@
         <v>0</v>
       </c>
       <c r="F440" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="441">
@@ -12505,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="F441" s="24" t="n">
-        <v>45476.5902199074</v>
+        <v>45476.75478009259</v>
       </c>
     </row>
     <row r="442">
@@ -12531,7 +12531,7 @@
         <v>0</v>
       </c>
       <c r="F442" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="443">
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="F443" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="444">
@@ -12583,7 +12583,7 @@
         <v>0</v>
       </c>
       <c r="F444" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="445">
@@ -12609,7 +12609,7 @@
         <v>0</v>
       </c>
       <c r="F445" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="446">
@@ -12635,7 +12635,7 @@
         <v>0</v>
       </c>
       <c r="F446" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="447">
@@ -12661,7 +12661,7 @@
         <v>0</v>
       </c>
       <c r="F447" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="448">
@@ -12687,7 +12687,7 @@
         <v>0</v>
       </c>
       <c r="F448" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="449">
@@ -12713,7 +12713,7 @@
         <v>0</v>
       </c>
       <c r="F449" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="450">
@@ -12739,7 +12739,7 @@
         <v>0</v>
       </c>
       <c r="F450" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="451">
@@ -12765,7 +12765,7 @@
         <v>0</v>
       </c>
       <c r="F451" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="452">
@@ -12791,7 +12791,7 @@
         <v>0</v>
       </c>
       <c r="F452" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="453">
@@ -12817,7 +12817,7 @@
         <v>0</v>
       </c>
       <c r="F453" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="454">
@@ -12843,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="F454" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="455">
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="F455" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="456">
@@ -12895,7 +12895,7 @@
         <v>0</v>
       </c>
       <c r="F456" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="457">
@@ -12921,7 +12921,7 @@
         <v>0</v>
       </c>
       <c r="F457" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="458">
@@ -12947,7 +12947,7 @@
         <v>0</v>
       </c>
       <c r="F458" s="24" t="n">
-        <v>45476.59023148148</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="459">
@@ -12973,7 +12973,7 @@
         <v>0</v>
       </c>
       <c r="F459" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="460">
@@ -12999,7 +12999,7 @@
         <v>0</v>
       </c>
       <c r="F460" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="461">
@@ -13025,7 +13025,7 @@
         <v>0</v>
       </c>
       <c r="F461" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="462">
@@ -13051,7 +13051,7 @@
         <v>0</v>
       </c>
       <c r="F462" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="463">
@@ -13077,7 +13077,7 @@
         <v>0</v>
       </c>
       <c r="F463" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="464">
@@ -13103,7 +13103,7 @@
         <v>0</v>
       </c>
       <c r="F464" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="465">
@@ -13129,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="F465" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="466">
@@ -13155,7 +13155,7 @@
         <v>0</v>
       </c>
       <c r="F466" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="467">
@@ -13181,7 +13181,7 @@
         <v>0</v>
       </c>
       <c r="F467" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="468">
@@ -13207,7 +13207,7 @@
         <v>0</v>
       </c>
       <c r="F468" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="469">
@@ -13233,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="F469" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="470">
@@ -13259,7 +13259,7 @@
         <v>0</v>
       </c>
       <c r="F470" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="471">
@@ -13285,7 +13285,7 @@
         <v>0</v>
       </c>
       <c r="F471" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="472">
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="F472" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="473">
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="F473" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="474">
@@ -13363,7 +13363,7 @@
         <v>0</v>
       </c>
       <c r="F474" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="475">
@@ -13389,7 +13389,7 @@
         <v>0</v>
       </c>
       <c r="F475" s="24" t="n">
-        <v>45476.59024305556</v>
+        <v>45476.75479166667</v>
       </c>
     </row>
     <row r="476">
@@ -13411,7 +13411,7 @@
         <v>0</v>
       </c>
       <c r="F476" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="477">
@@ -13437,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="F477" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="478">
@@ -13463,7 +13463,7 @@
         <v>0</v>
       </c>
       <c r="F478" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="479">
@@ -13489,7 +13489,7 @@
         <v>0</v>
       </c>
       <c r="F479" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="480">
@@ -13515,7 +13515,7 @@
         <v>0</v>
       </c>
       <c r="F480" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="481">
@@ -13541,7 +13541,7 @@
         <v>0</v>
       </c>
       <c r="F481" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="482">
@@ -13567,7 +13567,7 @@
         <v>0</v>
       </c>
       <c r="F482" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="483">
@@ -13593,7 +13593,7 @@
         <v>0</v>
       </c>
       <c r="F483" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="484">
@@ -13619,7 +13619,7 @@
         <v>0</v>
       </c>
       <c r="F484" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="485">
@@ -13645,7 +13645,7 @@
         <v>0</v>
       </c>
       <c r="F485" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="486">
@@ -13671,7 +13671,7 @@
         <v>0</v>
       </c>
       <c r="F486" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="487">
@@ -13697,7 +13697,7 @@
         <v>0</v>
       </c>
       <c r="F487" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="488">
@@ -13723,7 +13723,7 @@
         <v>0</v>
       </c>
       <c r="F488" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="489">
@@ -13749,7 +13749,7 @@
         <v>0</v>
       </c>
       <c r="F489" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="490">
@@ -13775,7 +13775,7 @@
         <v>0</v>
       </c>
       <c r="F490" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="491">
@@ -13801,7 +13801,7 @@
         <v>0</v>
       </c>
       <c r="F491" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="492">
@@ -13827,7 +13827,7 @@
         <v>0</v>
       </c>
       <c r="F492" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="493">
@@ -13853,7 +13853,7 @@
         <v>0</v>
       </c>
       <c r="F493" s="24" t="n">
-        <v>45476.59025462963</v>
+        <v>45476.75480324074</v>
       </c>
     </row>
     <row r="494">
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="F494" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="495">
@@ -13901,7 +13901,7 @@
         <v>0</v>
       </c>
       <c r="F495" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="496">
@@ -13927,7 +13927,7 @@
         <v>0</v>
       </c>
       <c r="F496" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="497">
@@ -13953,7 +13953,7 @@
         <v>0</v>
       </c>
       <c r="F497" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="498">
@@ -13979,7 +13979,7 @@
         <v>0</v>
       </c>
       <c r="F498" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="499">
@@ -14005,7 +14005,7 @@
         <v>0</v>
       </c>
       <c r="F499" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="500">
@@ -14031,7 +14031,7 @@
         <v>0</v>
       </c>
       <c r="F500" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="501">
@@ -14057,7 +14057,7 @@
         <v>0</v>
       </c>
       <c r="F501" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="502">
@@ -14083,7 +14083,7 @@
         <v>0</v>
       </c>
       <c r="F502" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="503">
@@ -14109,7 +14109,7 @@
         <v>0</v>
       </c>
       <c r="F503" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="504">
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="F504" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="505">
@@ -14161,7 +14161,7 @@
         <v>0</v>
       </c>
       <c r="F505" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="506">
@@ -14187,7 +14187,7 @@
         <v>0</v>
       </c>
       <c r="F506" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="507">
@@ -14213,7 +14213,7 @@
         <v>0</v>
       </c>
       <c r="F507" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="508">
@@ -14239,7 +14239,7 @@
         <v>0</v>
       </c>
       <c r="F508" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="509">
@@ -14265,7 +14265,7 @@
         <v>0</v>
       </c>
       <c r="F509" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="510">
@@ -14291,7 +14291,7 @@
         <v>0</v>
       </c>
       <c r="F510" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="511">
@@ -14317,7 +14317,7 @@
         <v>0</v>
       </c>
       <c r="F511" s="24" t="n">
-        <v>45476.5902662037</v>
+        <v>45476.75482638889</v>
       </c>
     </row>
     <row r="512">
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="F512" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="513">
@@ -14369,7 +14369,7 @@
         <v>0</v>
       </c>
       <c r="F513" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="514">
@@ -14395,7 +14395,7 @@
         <v>0</v>
       </c>
       <c r="F514" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="515">
@@ -14421,7 +14421,7 @@
         <v>0</v>
       </c>
       <c r="F515" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="516">
@@ -14447,7 +14447,7 @@
         <v>0</v>
       </c>
       <c r="F516" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="517">
@@ -14473,7 +14473,7 @@
         <v>0</v>
       </c>
       <c r="F517" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="518">
@@ -14499,7 +14499,7 @@
         <v>0</v>
       </c>
       <c r="F518" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="519">
@@ -14525,7 +14525,7 @@
         <v>0</v>
       </c>
       <c r="F519" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="520">
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="F520" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="521">
@@ -14577,7 +14577,7 @@
         <v>0</v>
       </c>
       <c r="F521" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="522">
@@ -14603,7 +14603,7 @@
         <v>0</v>
       </c>
       <c r="F522" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="523">
@@ -14629,7 +14629,7 @@
         <v>0</v>
       </c>
       <c r="F523" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="524">
@@ -14655,7 +14655,7 @@
         <v>0</v>
       </c>
       <c r="F524" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="525">
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="F525" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="526">
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="F526" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="527">
@@ -14733,7 +14733,7 @@
         <v>0</v>
       </c>
       <c r="F527" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
     <row r="528">
@@ -14759,7 +14759,7 @@
         <v>0</v>
       </c>
       <c r="F528" s="24" t="n">
-        <v>45476.59028935185</v>
+        <v>45476.75483796297</v>
       </c>
     </row>
   </sheetData>

--- a/kream_test_data.xlsx
+++ b/kream_test_data.xlsx
@@ -1099,7 +1099,7 @@
         <v>0</v>
       </c>
       <c r="F2" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="3">
@@ -1125,7 +1125,7 @@
         <v>0</v>
       </c>
       <c r="F3" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="4">
@@ -1151,7 +1151,7 @@
         <v>0</v>
       </c>
       <c r="F4" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="5">
@@ -1177,7 +1177,7 @@
         <v>0</v>
       </c>
       <c r="F5" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="6">
@@ -1203,7 +1203,7 @@
         <v>0</v>
       </c>
       <c r="F6" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="7">
@@ -1229,7 +1229,7 @@
         <v>0</v>
       </c>
       <c r="F7" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="8">
@@ -1255,7 +1255,7 @@
         <v>0</v>
       </c>
       <c r="F8" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="9">
@@ -1281,7 +1281,7 @@
         <v>0</v>
       </c>
       <c r="F9" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="10">
@@ -1307,7 +1307,7 @@
         <v>0</v>
       </c>
       <c r="F10" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="11">
@@ -1333,7 +1333,7 @@
         <v>0</v>
       </c>
       <c r="F11" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="12">
@@ -1359,7 +1359,7 @@
         <v>0</v>
       </c>
       <c r="F12" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="13">
@@ -1385,7 +1385,7 @@
         <v>0</v>
       </c>
       <c r="F13" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="14">
@@ -1411,7 +1411,7 @@
         <v>0</v>
       </c>
       <c r="F14" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="15">
@@ -1437,7 +1437,7 @@
         <v>0</v>
       </c>
       <c r="F15" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="16">
@@ -1463,7 +1463,7 @@
         <v>0</v>
       </c>
       <c r="F16" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="17">
@@ -1489,7 +1489,7 @@
         <v>0</v>
       </c>
       <c r="F17" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="18">
@@ -1515,7 +1515,7 @@
         <v>0</v>
       </c>
       <c r="F18" s="24" t="n">
-        <v>45476.75450231481</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="19">
@@ -1541,7 +1541,7 @@
         <v>0</v>
       </c>
       <c r="F19" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="20">
@@ -1567,7 +1567,7 @@
         <v>0</v>
       </c>
       <c r="F20" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="21">
@@ -1593,7 +1593,7 @@
         <v>0</v>
       </c>
       <c r="F21" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="22">
@@ -1619,7 +1619,7 @@
         <v>0</v>
       </c>
       <c r="F22" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="23">
@@ -1645,7 +1645,7 @@
         <v>0</v>
       </c>
       <c r="F23" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="24">
@@ -1671,7 +1671,7 @@
         <v>0</v>
       </c>
       <c r="F24" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="25">
@@ -1697,7 +1697,7 @@
         <v>0</v>
       </c>
       <c r="F25" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="26">
@@ -1723,7 +1723,7 @@
         <v>0</v>
       </c>
       <c r="F26" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="27">
@@ -1749,7 +1749,7 @@
         <v>0</v>
       </c>
       <c r="F27" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="28">
@@ -1775,7 +1775,7 @@
         <v>0</v>
       </c>
       <c r="F28" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="29">
@@ -1801,7 +1801,7 @@
         <v>0</v>
       </c>
       <c r="F29" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="30">
@@ -1827,7 +1827,7 @@
         <v>0</v>
       </c>
       <c r="F30" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="31">
@@ -1853,7 +1853,7 @@
         <v>0</v>
       </c>
       <c r="F31" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="32">
@@ -1879,7 +1879,7 @@
         <v>0</v>
       </c>
       <c r="F32" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="33">
@@ -1905,7 +1905,7 @@
         <v>0</v>
       </c>
       <c r="F33" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="34">
@@ -1931,7 +1931,7 @@
         <v>0</v>
       </c>
       <c r="F34" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="35">
@@ -1957,7 +1957,7 @@
         <v>0</v>
       </c>
       <c r="F35" s="24" t="n">
-        <v>45476.75451388889</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="36">
@@ -1983,7 +1983,7 @@
         <v>0</v>
       </c>
       <c r="F36" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="37">
@@ -2009,7 +2009,7 @@
         <v>0</v>
       </c>
       <c r="F37" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="38">
@@ -2035,7 +2035,7 @@
         <v>0</v>
       </c>
       <c r="F38" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="39">
@@ -2061,7 +2061,7 @@
         <v>0</v>
       </c>
       <c r="F39" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="40">
@@ -2087,7 +2087,7 @@
         <v>0</v>
       </c>
       <c r="F40" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="41">
@@ -2113,7 +2113,7 @@
         <v>0</v>
       </c>
       <c r="F41" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="42">
@@ -2139,7 +2139,7 @@
         <v>0</v>
       </c>
       <c r="F42" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="43">
@@ -2165,7 +2165,7 @@
         <v>0</v>
       </c>
       <c r="F43" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="44">
@@ -2191,7 +2191,7 @@
         <v>0</v>
       </c>
       <c r="F44" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="45">
@@ -2217,7 +2217,7 @@
         <v>0</v>
       </c>
       <c r="F45" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="46">
@@ -2243,7 +2243,7 @@
         <v>0</v>
       </c>
       <c r="F46" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="47">
@@ -2269,7 +2269,7 @@
         <v>0</v>
       </c>
       <c r="F47" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="48">
@@ -2295,7 +2295,7 @@
         <v>0</v>
       </c>
       <c r="F48" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="49">
@@ -2321,7 +2321,7 @@
         <v>0</v>
       </c>
       <c r="F49" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="50">
@@ -2347,7 +2347,7 @@
         <v>0</v>
       </c>
       <c r="F50" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="51">
@@ -2373,7 +2373,7 @@
         <v>0</v>
       </c>
       <c r="F51" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="52">
@@ -2399,7 +2399,7 @@
         <v>0</v>
       </c>
       <c r="F52" s="24" t="n">
-        <v>45476.75452546297</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="53">
@@ -2425,7 +2425,7 @@
         <v>0</v>
       </c>
       <c r="F53" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="54">
@@ -2451,7 +2451,7 @@
         <v>0</v>
       </c>
       <c r="F54" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="55">
@@ -2477,7 +2477,7 @@
         <v>0</v>
       </c>
       <c r="F55" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="56">
@@ -2503,7 +2503,7 @@
         <v>0</v>
       </c>
       <c r="F56" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="57">
@@ -2529,7 +2529,7 @@
         <v>0</v>
       </c>
       <c r="F57" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="58">
@@ -2555,7 +2555,7 @@
         <v>0</v>
       </c>
       <c r="F58" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="59">
@@ -2581,7 +2581,7 @@
         <v>0</v>
       </c>
       <c r="F59" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="60">
@@ -2607,7 +2607,7 @@
         <v>0</v>
       </c>
       <c r="F60" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="61">
@@ -2633,7 +2633,7 @@
         <v>0</v>
       </c>
       <c r="F61" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="62">
@@ -2659,7 +2659,7 @@
         <v>0</v>
       </c>
       <c r="F62" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="63">
@@ -2685,7 +2685,7 @@
         <v>0</v>
       </c>
       <c r="F63" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="64">
@@ -2711,7 +2711,7 @@
         <v>0</v>
       </c>
       <c r="F64" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="65">
@@ -2737,7 +2737,7 @@
         <v>0</v>
       </c>
       <c r="F65" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="66">
@@ -2763,7 +2763,7 @@
         <v>0</v>
       </c>
       <c r="F66" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="67">
@@ -2789,7 +2789,7 @@
         <v>0</v>
       </c>
       <c r="F67" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="68">
@@ -2815,7 +2815,7 @@
         <v>0</v>
       </c>
       <c r="F68" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="69">
@@ -2841,7 +2841,7 @@
         <v>0</v>
       </c>
       <c r="F69" s="24" t="n">
-        <v>45476.75453703704</v>
+        <v>45476.76313657407</v>
       </c>
     </row>
     <row r="70">
@@ -2867,7 +2867,7 @@
         <v>0</v>
       </c>
       <c r="F70" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="71">
@@ -2893,7 +2893,7 @@
         <v>0</v>
       </c>
       <c r="F71" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="72">
@@ -2919,7 +2919,7 @@
         <v>0</v>
       </c>
       <c r="F72" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="73">
@@ -2945,7 +2945,7 @@
         <v>0</v>
       </c>
       <c r="F73" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="74">
@@ -2971,7 +2971,7 @@
         <v>0</v>
       </c>
       <c r="F74" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="75">
@@ -2997,7 +2997,7 @@
         <v>0</v>
       </c>
       <c r="F75" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="76">
@@ -3023,7 +3023,7 @@
         <v>0</v>
       </c>
       <c r="F76" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="77">
@@ -3049,7 +3049,7 @@
         <v>0</v>
       </c>
       <c r="F77" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="78">
@@ -3075,7 +3075,7 @@
         <v>0</v>
       </c>
       <c r="F78" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="79">
@@ -3101,7 +3101,7 @@
         <v>0</v>
       </c>
       <c r="F79" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="80">
@@ -3127,7 +3127,7 @@
         <v>0</v>
       </c>
       <c r="F80" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="81">
@@ -3153,7 +3153,7 @@
         <v>0</v>
       </c>
       <c r="F81" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="82">
@@ -3179,7 +3179,7 @@
         <v>0</v>
       </c>
       <c r="F82" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="83">
@@ -3205,7 +3205,7 @@
         <v>0</v>
       </c>
       <c r="F83" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="84">
@@ -3231,7 +3231,7 @@
         <v>0</v>
       </c>
       <c r="F84" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="85">
@@ -3257,7 +3257,7 @@
         <v>0</v>
       </c>
       <c r="F85" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="86">
@@ -3283,7 +3283,7 @@
         <v>0</v>
       </c>
       <c r="F86" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="87">
@@ -3309,7 +3309,7 @@
         <v>0</v>
       </c>
       <c r="F87" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="88">
@@ -3335,7 +3335,7 @@
         <v>0</v>
       </c>
       <c r="F88" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="89">
@@ -3361,7 +3361,7 @@
         <v>0</v>
       </c>
       <c r="F89" s="24" t="n">
-        <v>45476.75454861111</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="90">
@@ -3387,7 +3387,7 @@
         <v>0</v>
       </c>
       <c r="F90" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="91">
@@ -3413,7 +3413,7 @@
         <v>0</v>
       </c>
       <c r="F91" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="92">
@@ -3439,7 +3439,7 @@
         <v>0</v>
       </c>
       <c r="F92" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="93">
@@ -3465,7 +3465,7 @@
         <v>0</v>
       </c>
       <c r="F93" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="94">
@@ -3491,7 +3491,7 @@
         <v>0</v>
       </c>
       <c r="F94" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="95">
@@ -3517,7 +3517,7 @@
         <v>0</v>
       </c>
       <c r="F95" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="96">
@@ -3543,7 +3543,7 @@
         <v>0</v>
       </c>
       <c r="F96" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="97">
@@ -3569,7 +3569,7 @@
         <v>0</v>
       </c>
       <c r="F97" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="98">
@@ -3595,7 +3595,7 @@
         <v>0</v>
       </c>
       <c r="F98" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="99">
@@ -3621,7 +3621,7 @@
         <v>0</v>
       </c>
       <c r="F99" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="100">
@@ -3647,7 +3647,7 @@
         <v>0</v>
       </c>
       <c r="F100" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="101">
@@ -3673,7 +3673,7 @@
         <v>0</v>
       </c>
       <c r="F101" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="102">
@@ -3699,7 +3699,7 @@
         <v>0</v>
       </c>
       <c r="F102" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="103">
@@ -3725,7 +3725,7 @@
         <v>0</v>
       </c>
       <c r="F103" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="104">
@@ -3751,7 +3751,7 @@
         <v>0</v>
       </c>
       <c r="F104" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="105">
@@ -3777,7 +3777,7 @@
         <v>0</v>
       </c>
       <c r="F105" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="106">
@@ -3803,7 +3803,7 @@
         <v>0</v>
       </c>
       <c r="F106" s="24" t="n">
-        <v>45476.75456018518</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="107">
@@ -3829,7 +3829,7 @@
         <v>0</v>
       </c>
       <c r="F107" s="24" t="n">
-        <v>45476.75457175926</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="108">
@@ -3855,7 +3855,7 @@
         <v>0</v>
       </c>
       <c r="F108" s="24" t="n">
-        <v>45476.75457175926</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="109">
@@ -3881,7 +3881,7 @@
         <v>0</v>
       </c>
       <c r="F109" s="24" t="n">
-        <v>45476.75457175926</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="110">
@@ -3907,7 +3907,7 @@
         <v>0</v>
       </c>
       <c r="F110" s="24" t="n">
-        <v>45476.75457175926</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="111">
@@ -3933,7 +3933,7 @@
         <v>0</v>
       </c>
       <c r="F111" s="24" t="n">
-        <v>45476.75457175926</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="112">
@@ -3959,7 +3959,7 @@
         <v>0</v>
       </c>
       <c r="F112" s="24" t="n">
-        <v>45476.75457175926</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="113">
@@ -3985,7 +3985,7 @@
         <v>0</v>
       </c>
       <c r="F113" s="24" t="n">
-        <v>45476.75457175926</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="114">
@@ -4011,7 +4011,7 @@
         <v>0</v>
       </c>
       <c r="F114" s="24" t="n">
-        <v>45476.75457175926</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="115">
@@ -4037,7 +4037,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="24" t="n">
-        <v>45476.75457175926</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="116">
@@ -4063,7 +4063,7 @@
         <v>0</v>
       </c>
       <c r="F116" s="24" t="n">
-        <v>45476.75457175926</v>
+        <v>45476.76314814815</v>
       </c>
     </row>
     <row r="117">
@@ -4089,7 +4089,7 @@
         <v>0</v>
       </c>
       <c r="F117" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="118">
@@ -4115,7 +4115,7 @@
         <v>0</v>
       </c>
       <c r="F118" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="119">
@@ -4141,7 +4141,7 @@
         <v>0</v>
       </c>
       <c r="F119" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="120">
@@ -4167,7 +4167,7 @@
         <v>0</v>
       </c>
       <c r="F120" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="121">
@@ -4193,7 +4193,7 @@
         <v>0</v>
       </c>
       <c r="F121" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="122">
@@ -4219,7 +4219,7 @@
         <v>0</v>
       </c>
       <c r="F122" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="123">
@@ -4245,7 +4245,7 @@
         <v>0</v>
       </c>
       <c r="F123" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="124">
@@ -4271,7 +4271,7 @@
         <v>0</v>
       </c>
       <c r="F124" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="125">
@@ -4297,7 +4297,7 @@
         <v>0</v>
       </c>
       <c r="F125" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="126">
@@ -4323,7 +4323,7 @@
         <v>0</v>
       </c>
       <c r="F126" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="127">
@@ -4349,7 +4349,7 @@
         <v>0</v>
       </c>
       <c r="F127" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="128">
@@ -4375,7 +4375,7 @@
         <v>0</v>
       </c>
       <c r="F128" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="129">
@@ -4401,7 +4401,7 @@
         <v>0</v>
       </c>
       <c r="F129" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="130">
@@ -4427,7 +4427,7 @@
         <v>0</v>
       </c>
       <c r="F130" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="131">
@@ -4453,7 +4453,7 @@
         <v>0</v>
       </c>
       <c r="F131" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="132">
@@ -4479,7 +4479,7 @@
         <v>0</v>
       </c>
       <c r="F132" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="133">
@@ -4505,7 +4505,7 @@
         <v>0</v>
       </c>
       <c r="F133" s="24" t="n">
-        <v>45476.75458333334</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="134">
@@ -4531,7 +4531,7 @@
         <v>0</v>
       </c>
       <c r="F134" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="135">
@@ -4557,7 +4557,7 @@
         <v>0</v>
       </c>
       <c r="F135" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="136">
@@ -4583,7 +4583,7 @@
         <v>0</v>
       </c>
       <c r="F136" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="137">
@@ -4609,7 +4609,7 @@
         <v>0</v>
       </c>
       <c r="F137" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="138">
@@ -4635,7 +4635,7 @@
         <v>0</v>
       </c>
       <c r="F138" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="139">
@@ -4661,7 +4661,7 @@
         <v>0</v>
       </c>
       <c r="F139" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="140">
@@ -4687,7 +4687,7 @@
         <v>0</v>
       </c>
       <c r="F140" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="141">
@@ -4713,7 +4713,7 @@
         <v>0</v>
       </c>
       <c r="F141" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="142">
@@ -4739,7 +4739,7 @@
         <v>0</v>
       </c>
       <c r="F142" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="143">
@@ -4765,7 +4765,7 @@
         <v>0</v>
       </c>
       <c r="F143" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="144">
@@ -4791,7 +4791,7 @@
         <v>0</v>
       </c>
       <c r="F144" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="145">
@@ -4817,7 +4817,7 @@
         <v>0</v>
       </c>
       <c r="F145" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="146">
@@ -4843,7 +4843,7 @@
         <v>0</v>
       </c>
       <c r="F146" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="147">
@@ -4869,7 +4869,7 @@
         <v>0</v>
       </c>
       <c r="F147" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="148">
@@ -4895,7 +4895,7 @@
         <v>0</v>
       </c>
       <c r="F148" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="149">
@@ -4921,7 +4921,7 @@
         <v>0</v>
       </c>
       <c r="F149" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="150">
@@ -4947,7 +4947,7 @@
         <v>0</v>
       </c>
       <c r="F150" s="24" t="n">
-        <v>45476.75460648148</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="151">
@@ -4973,7 +4973,7 @@
         <v>0</v>
       </c>
       <c r="F151" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="152">
@@ -4999,7 +4999,7 @@
         <v>0</v>
       </c>
       <c r="F152" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="153">
@@ -5025,7 +5025,7 @@
         <v>0</v>
       </c>
       <c r="F153" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="154">
@@ -5051,7 +5051,7 @@
         <v>0</v>
       </c>
       <c r="F154" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="155">
@@ -5077,7 +5077,7 @@
         <v>0</v>
       </c>
       <c r="F155" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="156">
@@ -5103,7 +5103,7 @@
         <v>0</v>
       </c>
       <c r="F156" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="157">
@@ -5129,7 +5129,7 @@
         <v>0</v>
       </c>
       <c r="F157" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="158">
@@ -5155,7 +5155,7 @@
         <v>0</v>
       </c>
       <c r="F158" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="159">
@@ -5181,7 +5181,7 @@
         <v>0</v>
       </c>
       <c r="F159" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="160">
@@ -5207,7 +5207,7 @@
         <v>0</v>
       </c>
       <c r="F160" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="161">
@@ -5233,7 +5233,7 @@
         <v>0</v>
       </c>
       <c r="F161" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="162">
@@ -5259,7 +5259,7 @@
         <v>0</v>
       </c>
       <c r="F162" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="163">
@@ -5285,7 +5285,7 @@
         <v>0</v>
       </c>
       <c r="F163" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="164">
@@ -5311,7 +5311,7 @@
         <v>0</v>
       </c>
       <c r="F164" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="165">
@@ -5337,7 +5337,7 @@
         <v>0</v>
       </c>
       <c r="F165" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="166">
@@ -5363,7 +5363,7 @@
         <v>0</v>
       </c>
       <c r="F166" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="167">
@@ -5389,7 +5389,7 @@
         <v>0</v>
       </c>
       <c r="F167" s="24" t="n">
-        <v>45476.75461805556</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="168">
@@ -5411,7 +5411,7 @@
         <v>0</v>
       </c>
       <c r="F168" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="169">
@@ -5437,7 +5437,7 @@
         <v>0</v>
       </c>
       <c r="F169" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="170">
@@ -5463,7 +5463,7 @@
         <v>0</v>
       </c>
       <c r="F170" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="171">
@@ -5489,7 +5489,7 @@
         <v>0</v>
       </c>
       <c r="F171" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="172">
@@ -5515,7 +5515,7 @@
         <v>0</v>
       </c>
       <c r="F172" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="173">
@@ -5541,7 +5541,7 @@
         <v>0</v>
       </c>
       <c r="F173" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="174">
@@ -5567,7 +5567,7 @@
         <v>0</v>
       </c>
       <c r="F174" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="175">
@@ -5593,7 +5593,7 @@
         <v>0</v>
       </c>
       <c r="F175" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="176">
@@ -5619,7 +5619,7 @@
         <v>0</v>
       </c>
       <c r="F176" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="177">
@@ -5645,7 +5645,7 @@
         <v>0</v>
       </c>
       <c r="F177" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="178">
@@ -5671,7 +5671,7 @@
         <v>0</v>
       </c>
       <c r="F178" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="179">
@@ -5697,7 +5697,7 @@
         <v>0</v>
       </c>
       <c r="F179" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="180">
@@ -5723,7 +5723,7 @@
         <v>0</v>
       </c>
       <c r="F180" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="181">
@@ -5749,7 +5749,7 @@
         <v>0</v>
       </c>
       <c r="F181" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="182">
@@ -5775,7 +5775,7 @@
         <v>0</v>
       </c>
       <c r="F182" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="183">
@@ -5801,7 +5801,7 @@
         <v>0</v>
       </c>
       <c r="F183" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="184">
@@ -5827,7 +5827,7 @@
         <v>0</v>
       </c>
       <c r="F184" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="185">
@@ -5853,7 +5853,7 @@
         <v>0</v>
       </c>
       <c r="F185" s="24" t="n">
-        <v>45476.75462962963</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="186">
@@ -5879,7 +5879,7 @@
         <v>0</v>
       </c>
       <c r="F186" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="187">
@@ -5905,7 +5905,7 @@
         <v>0</v>
       </c>
       <c r="F187" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="188">
@@ -5931,7 +5931,7 @@
         <v>0</v>
       </c>
       <c r="F188" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="189">
@@ -5957,7 +5957,7 @@
         <v>0</v>
       </c>
       <c r="F189" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="190">
@@ -5983,7 +5983,7 @@
         <v>0</v>
       </c>
       <c r="F190" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="191">
@@ -6009,7 +6009,7 @@
         <v>0</v>
       </c>
       <c r="F191" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="192">
@@ -6035,7 +6035,7 @@
         <v>0</v>
       </c>
       <c r="F192" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="193">
@@ -6061,7 +6061,7 @@
         <v>0</v>
       </c>
       <c r="F193" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="194">
@@ -6087,7 +6087,7 @@
         <v>0</v>
       </c>
       <c r="F194" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="195">
@@ -6113,7 +6113,7 @@
         <v>0</v>
       </c>
       <c r="F195" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="196">
@@ -6139,7 +6139,7 @@
         <v>0</v>
       </c>
       <c r="F196" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="197">
@@ -6165,7 +6165,7 @@
         <v>0</v>
       </c>
       <c r="F197" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="198">
@@ -6191,7 +6191,7 @@
         <v>0</v>
       </c>
       <c r="F198" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="199">
@@ -6217,7 +6217,7 @@
         <v>0</v>
       </c>
       <c r="F199" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="200">
@@ -6243,7 +6243,7 @@
         <v>0</v>
       </c>
       <c r="F200" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="201">
@@ -6269,7 +6269,7 @@
         <v>0</v>
       </c>
       <c r="F201" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="202">
@@ -6295,7 +6295,7 @@
         <v>0</v>
       </c>
       <c r="F202" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.76315972222</v>
       </c>
     </row>
     <row r="203">
@@ -6321,7 +6321,7 @@
         <v>0</v>
       </c>
       <c r="F203" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="204">
@@ -6347,7 +6347,7 @@
         <v>0</v>
       </c>
       <c r="F204" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="205">
@@ -6373,7 +6373,7 @@
         <v>0</v>
       </c>
       <c r="F205" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="206">
@@ -6399,7 +6399,7 @@
         <v>0</v>
       </c>
       <c r="F206" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="207">
@@ -6425,7 +6425,7 @@
         <v>0</v>
       </c>
       <c r="F207" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="208">
@@ -6451,7 +6451,7 @@
         <v>0</v>
       </c>
       <c r="F208" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="209">
@@ -6477,7 +6477,7 @@
         <v>0</v>
       </c>
       <c r="F209" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="210">
@@ -6503,7 +6503,7 @@
         <v>0</v>
       </c>
       <c r="F210" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="211">
@@ -6529,7 +6529,7 @@
         <v>0</v>
       </c>
       <c r="F211" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="212">
@@ -6555,7 +6555,7 @@
         <v>0</v>
       </c>
       <c r="F212" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="213">
@@ -6581,7 +6581,7 @@
         <v>0</v>
       </c>
       <c r="F213" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="214">
@@ -6607,7 +6607,7 @@
         <v>0</v>
       </c>
       <c r="F214" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="215">
@@ -6633,7 +6633,7 @@
         <v>0</v>
       </c>
       <c r="F215" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="216">
@@ -6659,7 +6659,7 @@
         <v>0</v>
       </c>
       <c r="F216" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="217">
@@ -6685,7 +6685,7 @@
         <v>0</v>
       </c>
       <c r="F217" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="218">
@@ -6711,7 +6711,7 @@
         <v>0</v>
       </c>
       <c r="F218" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="219">
@@ -6737,7 +6737,7 @@
         <v>0</v>
       </c>
       <c r="F219" s="24" t="n">
-        <v>45476.7546412037</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="220">
@@ -6763,7 +6763,7 @@
         <v>0</v>
       </c>
       <c r="F220" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="221">
@@ -6789,7 +6789,7 @@
         <v>0</v>
       </c>
       <c r="F221" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="222">
@@ -6815,7 +6815,7 @@
         <v>0</v>
       </c>
       <c r="F222" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="223">
@@ -6841,7 +6841,7 @@
         <v>0</v>
       </c>
       <c r="F223" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="224">
@@ -6867,7 +6867,7 @@
         <v>0</v>
       </c>
       <c r="F224" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="225">
@@ -6893,7 +6893,7 @@
         <v>0</v>
       </c>
       <c r="F225" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="226">
@@ -6919,7 +6919,7 @@
         <v>0</v>
       </c>
       <c r="F226" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="227">
@@ -6945,7 +6945,7 @@
         <v>0</v>
       </c>
       <c r="F227" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="228">
@@ -6971,7 +6971,7 @@
         <v>0</v>
       </c>
       <c r="F228" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="229">
@@ -6997,7 +6997,7 @@
         <v>0</v>
       </c>
       <c r="F229" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="230">
@@ -7023,7 +7023,7 @@
         <v>0</v>
       </c>
       <c r="F230" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="231">
@@ -7049,7 +7049,7 @@
         <v>0</v>
       </c>
       <c r="F231" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="232">
@@ -7075,7 +7075,7 @@
         <v>0</v>
       </c>
       <c r="F232" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="233">
@@ -7101,7 +7101,7 @@
         <v>0</v>
       </c>
       <c r="F233" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="234">
@@ -7127,7 +7127,7 @@
         <v>0</v>
       </c>
       <c r="F234" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="235">
@@ -7153,7 +7153,7 @@
         <v>0</v>
       </c>
       <c r="F235" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="236">
@@ -7179,7 +7179,7 @@
         <v>0</v>
       </c>
       <c r="F236" s="24" t="n">
-        <v>45476.75465277778</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="237">
@@ -7205,7 +7205,7 @@
         <v>0</v>
       </c>
       <c r="F237" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="238">
@@ -7231,7 +7231,7 @@
         <v>0</v>
       </c>
       <c r="F238" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="239">
@@ -7257,7 +7257,7 @@
         <v>0</v>
       </c>
       <c r="F239" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="240">
@@ -7283,7 +7283,7 @@
         <v>0</v>
       </c>
       <c r="F240" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="241">
@@ -7309,7 +7309,7 @@
         <v>0</v>
       </c>
       <c r="F241" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="242">
@@ -7335,7 +7335,7 @@
         <v>0</v>
       </c>
       <c r="F242" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="243">
@@ -7361,7 +7361,7 @@
         <v>0</v>
       </c>
       <c r="F243" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="244">
@@ -7387,7 +7387,7 @@
         <v>0</v>
       </c>
       <c r="F244" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="245">
@@ -7413,7 +7413,7 @@
         <v>0</v>
       </c>
       <c r="F245" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="246">
@@ -7439,7 +7439,7 @@
         <v>0</v>
       </c>
       <c r="F246" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="247">
@@ -7465,7 +7465,7 @@
         <v>0</v>
       </c>
       <c r="F247" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="248">
@@ -7491,7 +7491,7 @@
         <v>0</v>
       </c>
       <c r="F248" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="249">
@@ -7517,7 +7517,7 @@
         <v>0</v>
       </c>
       <c r="F249" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="250">
@@ -7543,7 +7543,7 @@
         <v>0</v>
       </c>
       <c r="F250" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="251">
@@ -7569,7 +7569,7 @@
         <v>0</v>
       </c>
       <c r="F251" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="252">
@@ -7595,7 +7595,7 @@
         <v>0</v>
       </c>
       <c r="F252" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="253">
@@ -7621,7 +7621,7 @@
         <v>0</v>
       </c>
       <c r="F253" s="24" t="n">
-        <v>45476.75466435185</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="254">
@@ -7647,7 +7647,7 @@
         <v>0</v>
       </c>
       <c r="F254" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="255">
@@ -7673,7 +7673,7 @@
         <v>0</v>
       </c>
       <c r="F255" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="256">
@@ -7699,7 +7699,7 @@
         <v>0</v>
       </c>
       <c r="F256" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="257">
@@ -7725,7 +7725,7 @@
         <v>0</v>
       </c>
       <c r="F257" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="258">
@@ -7751,7 +7751,7 @@
         <v>0</v>
       </c>
       <c r="F258" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="259">
@@ -7777,7 +7777,7 @@
         <v>0</v>
       </c>
       <c r="F259" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="260">
@@ -7803,7 +7803,7 @@
         <v>0</v>
       </c>
       <c r="F260" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="261">
@@ -7829,7 +7829,7 @@
         <v>0</v>
       </c>
       <c r="F261" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="262">
@@ -7855,7 +7855,7 @@
         <v>0</v>
       </c>
       <c r="F262" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="263">
@@ -7881,7 +7881,7 @@
         <v>0</v>
       </c>
       <c r="F263" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="264">
@@ -7907,7 +7907,7 @@
         <v>0</v>
       </c>
       <c r="F264" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="265">
@@ -7933,7 +7933,7 @@
         <v>0</v>
       </c>
       <c r="F265" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="266">
@@ -7959,7 +7959,7 @@
         <v>0</v>
       </c>
       <c r="F266" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="267">
@@ -7985,7 +7985,7 @@
         <v>0</v>
       </c>
       <c r="F267" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="268">
@@ -8011,7 +8011,7 @@
         <v>0</v>
       </c>
       <c r="F268" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="269">
@@ -8037,7 +8037,7 @@
         <v>0</v>
       </c>
       <c r="F269" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="270">
@@ -8063,7 +8063,7 @@
         <v>0</v>
       </c>
       <c r="F270" s="24" t="n">
-        <v>45476.75467592593</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="271">
@@ -8089,7 +8089,7 @@
         <v>0</v>
       </c>
       <c r="F271" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="272">
@@ -8115,7 +8115,7 @@
         <v>0</v>
       </c>
       <c r="F272" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="273">
@@ -8141,7 +8141,7 @@
         <v>0</v>
       </c>
       <c r="F273" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="274">
@@ -8167,7 +8167,7 @@
         <v>0</v>
       </c>
       <c r="F274" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="275">
@@ -8193,7 +8193,7 @@
         <v>0</v>
       </c>
       <c r="F275" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="276">
@@ -8219,7 +8219,7 @@
         <v>0</v>
       </c>
       <c r="F276" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="277">
@@ -8245,7 +8245,7 @@
         <v>0</v>
       </c>
       <c r="F277" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="278">
@@ -8271,7 +8271,7 @@
         <v>0</v>
       </c>
       <c r="F278" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="279">
@@ -8297,7 +8297,7 @@
         <v>0</v>
       </c>
       <c r="F279" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="280">
@@ -8323,7 +8323,7 @@
         <v>0</v>
       </c>
       <c r="F280" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="281">
@@ -8349,7 +8349,7 @@
         <v>0</v>
       </c>
       <c r="F281" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="282">
@@ -8375,7 +8375,7 @@
         <v>0</v>
       </c>
       <c r="F282" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="283">
@@ -8401,7 +8401,7 @@
         <v>0</v>
       </c>
       <c r="F283" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="284">
@@ -8427,7 +8427,7 @@
         <v>0</v>
       </c>
       <c r="F284" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="285">
@@ -8453,7 +8453,7 @@
         <v>0</v>
       </c>
       <c r="F285" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="286">
@@ -8479,7 +8479,7 @@
         <v>0</v>
       </c>
       <c r="F286" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="287">
@@ -8505,7 +8505,7 @@
         <v>0</v>
       </c>
       <c r="F287" s="24" t="n">
-        <v>45476.7546875</v>
+        <v>45476.7631712963</v>
       </c>
     </row>
     <row r="288">
@@ -8531,7 +8531,7 @@
         <v>0</v>
       </c>
       <c r="F288" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="289">
@@ -8557,7 +8557,7 @@
         <v>0</v>
       </c>
       <c r="F289" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="290">
@@ -8583,7 +8583,7 @@
         <v>0</v>
       </c>
       <c r="F290" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="291">
@@ -8609,7 +8609,7 @@
         <v>0</v>
       </c>
       <c r="F291" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="292">
@@ -8635,7 +8635,7 @@
         <v>0</v>
       </c>
       <c r="F292" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="293">
@@ -8661,7 +8661,7 @@
         <v>0</v>
       </c>
       <c r="F293" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="294">
@@ -8687,7 +8687,7 @@
         <v>0</v>
       </c>
       <c r="F294" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="295">
@@ -8713,7 +8713,7 @@
         <v>0</v>
       </c>
       <c r="F295" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="296">
@@ -8739,7 +8739,7 @@
         <v>0</v>
       </c>
       <c r="F296" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="297">
@@ -8765,7 +8765,7 @@
         <v>0</v>
       </c>
       <c r="F297" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="298">
@@ -8791,7 +8791,7 @@
         <v>0</v>
       </c>
       <c r="F298" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="299">
@@ -8817,7 +8817,7 @@
         <v>0</v>
       </c>
       <c r="F299" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="300">
@@ -8843,7 +8843,7 @@
         <v>0</v>
       </c>
       <c r="F300" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="301">
@@ -8869,7 +8869,7 @@
         <v>0</v>
       </c>
       <c r="F301" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="302">
@@ -8895,7 +8895,7 @@
         <v>0</v>
       </c>
       <c r="F302" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="303">
@@ -8921,7 +8921,7 @@
         <v>0</v>
       </c>
       <c r="F303" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="304">
@@ -8947,7 +8947,7 @@
         <v>0</v>
       </c>
       <c r="F304" s="24" t="n">
-        <v>45476.75469907407</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="305">
@@ -8973,7 +8973,7 @@
         <v>0</v>
       </c>
       <c r="F305" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="306">
@@ -8999,7 +8999,7 @@
         <v>0</v>
       </c>
       <c r="F306" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="307">
@@ -9025,7 +9025,7 @@
         <v>0</v>
       </c>
       <c r="F307" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="308">
@@ -9051,7 +9051,7 @@
         <v>0</v>
       </c>
       <c r="F308" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="309">
@@ -9077,7 +9077,7 @@
         <v>0</v>
       </c>
       <c r="F309" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="310">
@@ -9103,7 +9103,7 @@
         <v>0</v>
       </c>
       <c r="F310" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="311">
@@ -9129,7 +9129,7 @@
         <v>0</v>
       </c>
       <c r="F311" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="312">
@@ -9155,7 +9155,7 @@
         <v>0</v>
       </c>
       <c r="F312" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="313">
@@ -9181,7 +9181,7 @@
         <v>0</v>
       </c>
       <c r="F313" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="314">
@@ -9207,7 +9207,7 @@
         <v>0</v>
       </c>
       <c r="F314" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="315">
@@ -9233,7 +9233,7 @@
         <v>0</v>
       </c>
       <c r="F315" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="316">
@@ -9259,7 +9259,7 @@
         <v>0</v>
       </c>
       <c r="F316" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="317">
@@ -9285,7 +9285,7 @@
         <v>0</v>
       </c>
       <c r="F317" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="318">
@@ -9311,7 +9311,7 @@
         <v>0</v>
       </c>
       <c r="F318" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="319">
@@ -9337,7 +9337,7 @@
         <v>0</v>
       </c>
       <c r="F319" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="320">
@@ -9363,7 +9363,7 @@
         <v>0</v>
       </c>
       <c r="F320" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="321">
@@ -9389,7 +9389,7 @@
         <v>0</v>
       </c>
       <c r="F321" s="24" t="n">
-        <v>45476.75471064815</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="322">
@@ -9411,7 +9411,7 @@
         <v>0</v>
       </c>
       <c r="F322" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="323">
@@ -9437,7 +9437,7 @@
         <v>0</v>
       </c>
       <c r="F323" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="324">
@@ -9463,7 +9463,7 @@
         <v>0</v>
       </c>
       <c r="F324" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="325">
@@ -9489,7 +9489,7 @@
         <v>0</v>
       </c>
       <c r="F325" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="326">
@@ -9515,7 +9515,7 @@
         <v>0</v>
       </c>
       <c r="F326" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="327">
@@ -9541,7 +9541,7 @@
         <v>0</v>
       </c>
       <c r="F327" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="328">
@@ -9567,7 +9567,7 @@
         <v>0</v>
       </c>
       <c r="F328" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="329">
@@ -9593,7 +9593,7 @@
         <v>0</v>
       </c>
       <c r="F329" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="330">
@@ -9619,7 +9619,7 @@
         <v>0</v>
       </c>
       <c r="F330" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="331">
@@ -9645,7 +9645,7 @@
         <v>0</v>
       </c>
       <c r="F331" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="332">
@@ -9671,7 +9671,7 @@
         <v>0</v>
       </c>
       <c r="F332" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="333">
@@ -9697,7 +9697,7 @@
         <v>0</v>
       </c>
       <c r="F333" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="334">
@@ -9723,7 +9723,7 @@
         <v>0</v>
       </c>
       <c r="F334" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="335">
@@ -9749,7 +9749,7 @@
         <v>0</v>
       </c>
       <c r="F335" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="336">
@@ -9775,7 +9775,7 @@
         <v>0</v>
       </c>
       <c r="F336" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="337">
@@ -9801,7 +9801,7 @@
         <v>0</v>
       </c>
       <c r="F337" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="338">
@@ -9827,7 +9827,7 @@
         <v>0</v>
       </c>
       <c r="F338" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="339">
@@ -9853,7 +9853,7 @@
         <v>0</v>
       </c>
       <c r="F339" s="24" t="n">
-        <v>45476.75472222222</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="340">
@@ -9879,7 +9879,7 @@
         <v>0</v>
       </c>
       <c r="F340" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="341">
@@ -9905,7 +9905,7 @@
         <v>0</v>
       </c>
       <c r="F341" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="342">
@@ -9931,7 +9931,7 @@
         <v>0</v>
       </c>
       <c r="F342" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="343">
@@ -9957,7 +9957,7 @@
         <v>0</v>
       </c>
       <c r="F343" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="344">
@@ -9983,7 +9983,7 @@
         <v>0</v>
       </c>
       <c r="F344" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="345">
@@ -10009,7 +10009,7 @@
         <v>0</v>
       </c>
       <c r="F345" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="346">
@@ -10035,7 +10035,7 @@
         <v>0</v>
       </c>
       <c r="F346" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="347">
@@ -10061,7 +10061,7 @@
         <v>0</v>
       </c>
       <c r="F347" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="348">
@@ -10087,7 +10087,7 @@
         <v>0</v>
       </c>
       <c r="F348" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="349">
@@ -10113,7 +10113,7 @@
         <v>0</v>
       </c>
       <c r="F349" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="350">
@@ -10139,7 +10139,7 @@
         <v>0</v>
       </c>
       <c r="F350" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="351">
@@ -10165,7 +10165,7 @@
         <v>0</v>
       </c>
       <c r="F351" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="352">
@@ -10191,7 +10191,7 @@
         <v>0</v>
       </c>
       <c r="F352" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="353">
@@ -10217,7 +10217,7 @@
         <v>0</v>
       </c>
       <c r="F353" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="354">
@@ -10243,7 +10243,7 @@
         <v>0</v>
       </c>
       <c r="F354" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="355">
@@ -10269,7 +10269,7 @@
         <v>0</v>
       </c>
       <c r="F355" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="356">
@@ -10295,7 +10295,7 @@
         <v>0</v>
       </c>
       <c r="F356" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="357">
@@ -10321,7 +10321,7 @@
         <v>0</v>
       </c>
       <c r="F357" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="358">
@@ -10347,7 +10347,7 @@
         <v>0</v>
       </c>
       <c r="F358" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="359">
@@ -10373,7 +10373,7 @@
         <v>0</v>
       </c>
       <c r="F359" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="360">
@@ -10399,7 +10399,7 @@
         <v>0</v>
       </c>
       <c r="F360" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="361">
@@ -10425,7 +10425,7 @@
         <v>0</v>
       </c>
       <c r="F361" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="362">
@@ -10451,7 +10451,7 @@
         <v>0</v>
       </c>
       <c r="F362" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="363">
@@ -10477,7 +10477,7 @@
         <v>0</v>
       </c>
       <c r="F363" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="364">
@@ -10503,7 +10503,7 @@
         <v>0</v>
       </c>
       <c r="F364" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="365">
@@ -10529,7 +10529,7 @@
         <v>0</v>
       </c>
       <c r="F365" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="366">
@@ -10555,7 +10555,7 @@
         <v>0</v>
       </c>
       <c r="F366" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="367">
@@ -10581,7 +10581,7 @@
         <v>0</v>
       </c>
       <c r="F367" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="368">
@@ -10607,7 +10607,7 @@
         <v>0</v>
       </c>
       <c r="F368" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="369">
@@ -10633,7 +10633,7 @@
         <v>0</v>
       </c>
       <c r="F369" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="370">
@@ -10659,7 +10659,7 @@
         <v>0</v>
       </c>
       <c r="F370" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="371">
@@ -10685,7 +10685,7 @@
         <v>0</v>
       </c>
       <c r="F371" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="372">
@@ -10711,7 +10711,7 @@
         <v>0</v>
       </c>
       <c r="F372" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="373">
@@ -10737,7 +10737,7 @@
         <v>0</v>
       </c>
       <c r="F373" s="24" t="n">
-        <v>45476.7547337963</v>
+        <v>45476.76318287037</v>
       </c>
     </row>
     <row r="374">
@@ -10763,7 +10763,7 @@
         <v>0</v>
       </c>
       <c r="F374" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="375">
@@ -10789,7 +10789,7 @@
         <v>0</v>
       </c>
       <c r="F375" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="376">
@@ -10815,7 +10815,7 @@
         <v>0</v>
       </c>
       <c r="F376" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="377">
@@ -10841,7 +10841,7 @@
         <v>0</v>
       </c>
       <c r="F377" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="378">
@@ -10867,7 +10867,7 @@
         <v>0</v>
       </c>
       <c r="F378" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="379">
@@ -10893,7 +10893,7 @@
         <v>0</v>
       </c>
       <c r="F379" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="380">
@@ -10919,7 +10919,7 @@
         <v>0</v>
       </c>
       <c r="F380" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="381">
@@ -10945,7 +10945,7 @@
         <v>0</v>
       </c>
       <c r="F381" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="382">
@@ -10971,7 +10971,7 @@
         <v>0</v>
       </c>
       <c r="F382" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="383">
@@ -10997,7 +10997,7 @@
         <v>0</v>
       </c>
       <c r="F383" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="384">
@@ -11023,7 +11023,7 @@
         <v>0</v>
       </c>
       <c r="F384" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="385">
@@ -11049,7 +11049,7 @@
         <v>0</v>
       </c>
       <c r="F385" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="386">
@@ -11075,7 +11075,7 @@
         <v>0</v>
       </c>
       <c r="F386" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="387">
@@ -11101,7 +11101,7 @@
         <v>0</v>
       </c>
       <c r="F387" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="388">
@@ -11127,7 +11127,7 @@
         <v>0</v>
       </c>
       <c r="F388" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="389">
@@ -11153,7 +11153,7 @@
         <v>0</v>
       </c>
       <c r="F389" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="390">
@@ -11179,7 +11179,7 @@
         <v>0</v>
       </c>
       <c r="F390" s="24" t="n">
-        <v>45476.75474537037</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="391">
@@ -11205,7 +11205,7 @@
         <v>0</v>
       </c>
       <c r="F391" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="392">
@@ -11231,7 +11231,7 @@
         <v>0</v>
       </c>
       <c r="F392" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="393">
@@ -11257,7 +11257,7 @@
         <v>0</v>
       </c>
       <c r="F393" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="394">
@@ -11283,7 +11283,7 @@
         <v>0</v>
       </c>
       <c r="F394" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="395">
@@ -11309,7 +11309,7 @@
         <v>0</v>
       </c>
       <c r="F395" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="396">
@@ -11335,7 +11335,7 @@
         <v>0</v>
       </c>
       <c r="F396" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="397">
@@ -11361,7 +11361,7 @@
         <v>0</v>
       </c>
       <c r="F397" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="398">
@@ -11387,7 +11387,7 @@
         <v>0</v>
       </c>
       <c r="F398" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="399">
@@ -11413,7 +11413,7 @@
         <v>0</v>
       </c>
       <c r="F399" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="400">
@@ -11439,7 +11439,7 @@
         <v>0</v>
       </c>
       <c r="F400" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="401">
@@ -11465,7 +11465,7 @@
         <v>0</v>
       </c>
       <c r="F401" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="402">
@@ -11491,7 +11491,7 @@
         <v>0</v>
       </c>
       <c r="F402" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="403">
@@ -11517,7 +11517,7 @@
         <v>0</v>
       </c>
       <c r="F403" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="404">
@@ -11543,7 +11543,7 @@
         <v>0</v>
       </c>
       <c r="F404" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="405">
@@ -11569,7 +11569,7 @@
         <v>0</v>
       </c>
       <c r="F405" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="406">
@@ -11595,7 +11595,7 @@
         <v>0</v>
       </c>
       <c r="F406" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="407">
@@ -11621,7 +11621,7 @@
         <v>0</v>
       </c>
       <c r="F407" s="24" t="n">
-        <v>45476.75475694444</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="408">
@@ -11647,7 +11647,7 @@
         <v>0</v>
       </c>
       <c r="F408" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="409">
@@ -11673,7 +11673,7 @@
         <v>0</v>
       </c>
       <c r="F409" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="410">
@@ -11699,7 +11699,7 @@
         <v>0</v>
       </c>
       <c r="F410" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="411">
@@ -11725,7 +11725,7 @@
         <v>0</v>
       </c>
       <c r="F411" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="412">
@@ -11751,7 +11751,7 @@
         <v>0</v>
       </c>
       <c r="F412" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="413">
@@ -11777,7 +11777,7 @@
         <v>0</v>
       </c>
       <c r="F413" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="414">
@@ -11803,7 +11803,7 @@
         <v>0</v>
       </c>
       <c r="F414" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="415">
@@ -11829,7 +11829,7 @@
         <v>0</v>
       </c>
       <c r="F415" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="416">
@@ -11855,7 +11855,7 @@
         <v>0</v>
       </c>
       <c r="F416" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="417">
@@ -11881,7 +11881,7 @@
         <v>0</v>
       </c>
       <c r="F417" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="418">
@@ -11907,7 +11907,7 @@
         <v>0</v>
       </c>
       <c r="F418" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="419">
@@ -11933,7 +11933,7 @@
         <v>0</v>
       </c>
       <c r="F419" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="420">
@@ -11959,7 +11959,7 @@
         <v>0</v>
       </c>
       <c r="F420" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="421">
@@ -11985,7 +11985,7 @@
         <v>0</v>
       </c>
       <c r="F421" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="422">
@@ -12011,7 +12011,7 @@
         <v>0</v>
       </c>
       <c r="F422" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="423">
@@ -12037,7 +12037,7 @@
         <v>0</v>
       </c>
       <c r="F423" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="424">
@@ -12063,7 +12063,7 @@
         <v>0</v>
       </c>
       <c r="F424" s="24" t="n">
-        <v>45476.75476851852</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="425">
@@ -12089,7 +12089,7 @@
         <v>0</v>
       </c>
       <c r="F425" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="426">
@@ -12115,7 +12115,7 @@
         <v>0</v>
       </c>
       <c r="F426" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="427">
@@ -12141,7 +12141,7 @@
         <v>0</v>
       </c>
       <c r="F427" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="428">
@@ -12167,7 +12167,7 @@
         <v>0</v>
       </c>
       <c r="F428" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="429">
@@ -12193,7 +12193,7 @@
         <v>0</v>
       </c>
       <c r="F429" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="430">
@@ -12219,7 +12219,7 @@
         <v>0</v>
       </c>
       <c r="F430" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="431">
@@ -12245,7 +12245,7 @@
         <v>0</v>
       </c>
       <c r="F431" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="432">
@@ -12271,7 +12271,7 @@
         <v>0</v>
       </c>
       <c r="F432" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="433">
@@ -12297,7 +12297,7 @@
         <v>0</v>
       </c>
       <c r="F433" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="434">
@@ -12323,7 +12323,7 @@
         <v>0</v>
       </c>
       <c r="F434" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="435">
@@ -12349,7 +12349,7 @@
         <v>0</v>
       </c>
       <c r="F435" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="436">
@@ -12375,7 +12375,7 @@
         <v>0</v>
       </c>
       <c r="F436" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="437">
@@ -12401,7 +12401,7 @@
         <v>0</v>
       </c>
       <c r="F437" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="438">
@@ -12427,7 +12427,7 @@
         <v>0</v>
       </c>
       <c r="F438" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="439">
@@ -12453,7 +12453,7 @@
         <v>0</v>
       </c>
       <c r="F439" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="440">
@@ -12479,7 +12479,7 @@
         <v>0</v>
       </c>
       <c r="F440" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="441">
@@ -12505,7 +12505,7 @@
         <v>0</v>
       </c>
       <c r="F441" s="24" t="n">
-        <v>45476.75478009259</v>
+        <v>45476.76319444444</v>
       </c>
     </row>
     <row r="442">
@@ -12531,7 +12531,7 @@
         <v>0</v>
       </c>
       <c r="F442" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="443">
@@ -12557,7 +12557,7 @@
         <v>0</v>
       </c>
       <c r="F443" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="444">
@@ -12583,7 +12583,7 @@
         <v>0</v>
       </c>
       <c r="F444" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="445">
@@ -12609,7 +12609,7 @@
         <v>0</v>
       </c>
       <c r="F445" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="446">
@@ -12635,7 +12635,7 @@
         <v>0</v>
       </c>
       <c r="F446" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="447">
@@ -12661,7 +12661,7 @@
         <v>0</v>
       </c>
       <c r="F447" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="448">
@@ -12687,7 +12687,7 @@
         <v>0</v>
       </c>
       <c r="F448" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="449">
@@ -12713,7 +12713,7 @@
         <v>0</v>
       </c>
       <c r="F449" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="450">
@@ -12739,7 +12739,7 @@
         <v>0</v>
       </c>
       <c r="F450" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="451">
@@ -12765,7 +12765,7 @@
         <v>0</v>
       </c>
       <c r="F451" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="452">
@@ -12791,7 +12791,7 @@
         <v>0</v>
       </c>
       <c r="F452" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="453">
@@ -12817,7 +12817,7 @@
         <v>0</v>
       </c>
       <c r="F453" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="454">
@@ -12843,7 +12843,7 @@
         <v>0</v>
       </c>
       <c r="F454" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="455">
@@ -12869,7 +12869,7 @@
         <v>0</v>
       </c>
       <c r="F455" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="456">
@@ -12895,7 +12895,7 @@
         <v>0</v>
       </c>
       <c r="F456" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="457">
@@ -12921,7 +12921,7 @@
         <v>0</v>
       </c>
       <c r="F457" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="458">
@@ -12947,7 +12947,7 @@
         <v>0</v>
       </c>
       <c r="F458" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="459">
@@ -12973,7 +12973,7 @@
         <v>0</v>
       </c>
       <c r="F459" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="460">
@@ -12999,7 +12999,7 @@
         <v>0</v>
       </c>
       <c r="F460" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="461">
@@ -13025,7 +13025,7 @@
         <v>0</v>
       </c>
       <c r="F461" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="462">
@@ -13051,7 +13051,7 @@
         <v>0</v>
       </c>
       <c r="F462" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="463">
@@ -13077,7 +13077,7 @@
         <v>0</v>
       </c>
       <c r="F463" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="464">
@@ -13103,7 +13103,7 @@
         <v>0</v>
       </c>
       <c r="F464" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="465">
@@ -13129,7 +13129,7 @@
         <v>0</v>
       </c>
       <c r="F465" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="466">
@@ -13155,7 +13155,7 @@
         <v>0</v>
       </c>
       <c r="F466" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="467">
@@ -13181,7 +13181,7 @@
         <v>0</v>
       </c>
       <c r="F467" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="468">
@@ -13207,7 +13207,7 @@
         <v>0</v>
       </c>
       <c r="F468" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="469">
@@ -13233,7 +13233,7 @@
         <v>0</v>
       </c>
       <c r="F469" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="470">
@@ -13259,7 +13259,7 @@
         <v>0</v>
       </c>
       <c r="F470" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="471">
@@ -13285,7 +13285,7 @@
         <v>0</v>
       </c>
       <c r="F471" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="472">
@@ -13311,7 +13311,7 @@
         <v>0</v>
       </c>
       <c r="F472" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="473">
@@ -13337,7 +13337,7 @@
         <v>0</v>
       </c>
       <c r="F473" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="474">
@@ -13363,7 +13363,7 @@
         <v>0</v>
       </c>
       <c r="F474" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="475">
@@ -13389,7 +13389,7 @@
         <v>0</v>
       </c>
       <c r="F475" s="24" t="n">
-        <v>45476.75479166667</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="476">
@@ -13411,7 +13411,7 @@
         <v>0</v>
       </c>
       <c r="F476" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="477">
@@ -13437,7 +13437,7 @@
         <v>0</v>
       </c>
       <c r="F477" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="478">
@@ -13463,7 +13463,7 @@
         <v>0</v>
       </c>
       <c r="F478" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="479">
@@ -13489,7 +13489,7 @@
         <v>0</v>
       </c>
       <c r="F479" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="480">
@@ -13515,7 +13515,7 @@
         <v>0</v>
       </c>
       <c r="F480" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="481">
@@ -13541,7 +13541,7 @@
         <v>0</v>
       </c>
       <c r="F481" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="482">
@@ -13567,7 +13567,7 @@
         <v>0</v>
       </c>
       <c r="F482" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="483">
@@ -13593,7 +13593,7 @@
         <v>0</v>
       </c>
       <c r="F483" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="484">
@@ -13619,7 +13619,7 @@
         <v>0</v>
       </c>
       <c r="F484" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="485">
@@ -13645,7 +13645,7 @@
         <v>0</v>
       </c>
       <c r="F485" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="486">
@@ -13671,7 +13671,7 @@
         <v>0</v>
       </c>
       <c r="F486" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="487">
@@ -13697,7 +13697,7 @@
         <v>0</v>
       </c>
       <c r="F487" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="488">
@@ -13723,7 +13723,7 @@
         <v>0</v>
       </c>
       <c r="F488" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="489">
@@ -13749,7 +13749,7 @@
         <v>0</v>
       </c>
       <c r="F489" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="490">
@@ -13775,7 +13775,7 @@
         <v>0</v>
       </c>
       <c r="F490" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="491">
@@ -13801,7 +13801,7 @@
         <v>0</v>
       </c>
       <c r="F491" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="492">
@@ -13827,7 +13827,7 @@
         <v>0</v>
       </c>
       <c r="F492" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="493">
@@ -13853,7 +13853,7 @@
         <v>0</v>
       </c>
       <c r="F493" s="24" t="n">
-        <v>45476.75480324074</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="494">
@@ -13875,7 +13875,7 @@
         <v>0</v>
       </c>
       <c r="F494" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="495">
@@ -13901,7 +13901,7 @@
         <v>0</v>
       </c>
       <c r="F495" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="496">
@@ -13927,7 +13927,7 @@
         <v>0</v>
       </c>
       <c r="F496" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="497">
@@ -13953,7 +13953,7 @@
         <v>0</v>
       </c>
       <c r="F497" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="498">
@@ -13979,7 +13979,7 @@
         <v>0</v>
       </c>
       <c r="F498" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="499">
@@ -14005,7 +14005,7 @@
         <v>0</v>
       </c>
       <c r="F499" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="500">
@@ -14031,7 +14031,7 @@
         <v>0</v>
       </c>
       <c r="F500" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="501">
@@ -14057,7 +14057,7 @@
         <v>0</v>
       </c>
       <c r="F501" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="502">
@@ -14083,7 +14083,7 @@
         <v>0</v>
       </c>
       <c r="F502" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="503">
@@ -14109,7 +14109,7 @@
         <v>0</v>
       </c>
       <c r="F503" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="504">
@@ -14135,7 +14135,7 @@
         <v>0</v>
       </c>
       <c r="F504" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="505">
@@ -14161,7 +14161,7 @@
         <v>0</v>
       </c>
       <c r="F505" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="506">
@@ -14187,7 +14187,7 @@
         <v>0</v>
       </c>
       <c r="F506" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="507">
@@ -14213,7 +14213,7 @@
         <v>0</v>
       </c>
       <c r="F507" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="508">
@@ -14239,7 +14239,7 @@
         <v>0</v>
       </c>
       <c r="F508" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="509">
@@ -14265,7 +14265,7 @@
         <v>0</v>
       </c>
       <c r="F509" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="510">
@@ -14291,7 +14291,7 @@
         <v>0</v>
       </c>
       <c r="F510" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="511">
@@ -14317,7 +14317,7 @@
         <v>0</v>
       </c>
       <c r="F511" s="24" t="n">
-        <v>45476.75482638889</v>
+        <v>45476.76320601852</v>
       </c>
     </row>
     <row r="512">
@@ -14343,7 +14343,7 @@
         <v>0</v>
       </c>
       <c r="F512" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="513">
@@ -14369,7 +14369,7 @@
         <v>0</v>
       </c>
       <c r="F513" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="514">
@@ -14395,7 +14395,7 @@
         <v>0</v>
       </c>
       <c r="F514" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="515">
@@ -14421,7 +14421,7 @@
         <v>0</v>
       </c>
       <c r="F515" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="516">
@@ -14447,7 +14447,7 @@
         <v>0</v>
       </c>
       <c r="F516" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="517">
@@ -14473,7 +14473,7 @@
         <v>0</v>
       </c>
       <c r="F517" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="518">
@@ -14499,7 +14499,7 @@
         <v>0</v>
       </c>
       <c r="F518" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="519">
@@ -14525,7 +14525,7 @@
         <v>0</v>
       </c>
       <c r="F519" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="520">
@@ -14551,7 +14551,7 @@
         <v>0</v>
       </c>
       <c r="F520" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="521">
@@ -14577,7 +14577,7 @@
         <v>0</v>
       </c>
       <c r="F521" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="522">
@@ -14603,7 +14603,7 @@
         <v>0</v>
       </c>
       <c r="F522" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="523">
@@ -14629,7 +14629,7 @@
         <v>0</v>
       </c>
       <c r="F523" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="524">
@@ -14655,7 +14655,7 @@
         <v>0</v>
       </c>
       <c r="F524" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="525">
@@ -14681,7 +14681,7 @@
         <v>0</v>
       </c>
       <c r="F525" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="526">
@@ -14707,7 +14707,7 @@
         <v>0</v>
       </c>
       <c r="F526" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="527">
@@ -14733,7 +14733,7 @@
         <v>0</v>
       </c>
       <c r="F527" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
     <row r="528">
@@ -14759,7 +14759,7 @@
         <v>0</v>
       </c>
       <c r="F528" s="24" t="n">
-        <v>45476.75483796297</v>
+        <v>45476.76321759259</v>
       </c>
     </row>
   </sheetData>
